--- a/output/version3/test/10-5/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
+++ b/output/version3/test/10-5/MARL/IL/RL-RL (+comm)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>493</v>
+        <v>529</v>
       </c>
       <c r="C2" t="n">
-        <v>475</v>
+        <v>480</v>
       </c>
       <c r="D2" t="n">
-        <v>484</v>
+        <v>430</v>
       </c>
       <c r="E2" t="n">
-        <v>421</v>
+        <v>459</v>
       </c>
       <c r="F2" t="n">
-        <v>447</v>
+        <v>418</v>
       </c>
       <c r="G2" t="n">
-        <v>396</v>
+        <v>459</v>
       </c>
       <c r="H2" t="n">
-        <v>470</v>
+        <v>462</v>
       </c>
       <c r="I2" t="n">
-        <v>468</v>
+        <v>502</v>
       </c>
       <c r="J2" t="n">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="K2" t="n">
-        <v>442</v>
+        <v>459</v>
       </c>
       <c r="L2" t="n">
-        <v>450.6</v>
+        <v>461.3</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>438</v>
+        <v>463</v>
       </c>
       <c r="C3" t="n">
-        <v>536</v>
+        <v>512</v>
       </c>
       <c r="D3" t="n">
-        <v>460</v>
+        <v>572</v>
       </c>
       <c r="E3" t="n">
-        <v>479</v>
+        <v>608</v>
       </c>
       <c r="F3" t="n">
-        <v>457</v>
+        <v>464</v>
       </c>
       <c r="G3" t="n">
-        <v>549</v>
+        <v>473</v>
       </c>
       <c r="H3" t="n">
-        <v>464</v>
+        <v>604</v>
       </c>
       <c r="I3" t="n">
-        <v>444</v>
+        <v>481</v>
       </c>
       <c r="J3" t="n">
-        <v>442</v>
+        <v>581</v>
       </c>
       <c r="K3" t="n">
-        <v>500</v>
+        <v>473</v>
       </c>
       <c r="L3" t="n">
-        <v>476.9</v>
+        <v>523.1</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>548</v>
+        <v>579</v>
       </c>
       <c r="C4" t="n">
-        <v>500</v>
+        <v>522</v>
       </c>
       <c r="D4" t="n">
         <v>460</v>
       </c>
       <c r="E4" t="n">
-        <v>508</v>
+        <v>467</v>
       </c>
       <c r="F4" t="n">
-        <v>521</v>
+        <v>588</v>
       </c>
       <c r="G4" t="n">
-        <v>550</v>
+        <v>531</v>
       </c>
       <c r="H4" t="n">
-        <v>527</v>
+        <v>470</v>
       </c>
       <c r="I4" t="n">
-        <v>505</v>
+        <v>450</v>
       </c>
       <c r="J4" t="n">
-        <v>473</v>
+        <v>491</v>
       </c>
       <c r="K4" t="n">
-        <v>464</v>
+        <v>533</v>
       </c>
       <c r="L4" t="n">
-        <v>505.6</v>
+        <v>509.1</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>486</v>
+        <v>452</v>
       </c>
       <c r="C5" t="n">
-        <v>458</v>
+        <v>530</v>
       </c>
       <c r="D5" t="n">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="E5" t="n">
-        <v>451</v>
+        <v>516</v>
       </c>
       <c r="F5" t="n">
-        <v>497</v>
+        <v>455</v>
       </c>
       <c r="G5" t="n">
-        <v>444</v>
+        <v>487</v>
       </c>
       <c r="H5" t="n">
-        <v>531</v>
+        <v>478</v>
       </c>
       <c r="I5" t="n">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="J5" t="n">
-        <v>459</v>
+        <v>524</v>
       </c>
       <c r="K5" t="n">
-        <v>527</v>
+        <v>484</v>
       </c>
       <c r="L5" t="n">
-        <v>482</v>
+        <v>488.2</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>453</v>
+        <v>413</v>
       </c>
       <c r="C6" t="n">
-        <v>456</v>
+        <v>518</v>
       </c>
       <c r="D6" t="n">
-        <v>435</v>
+        <v>461</v>
       </c>
       <c r="E6" t="n">
-        <v>509</v>
+        <v>512</v>
       </c>
       <c r="F6" t="n">
-        <v>452</v>
+        <v>427</v>
       </c>
       <c r="G6" t="n">
-        <v>505</v>
+        <v>424</v>
       </c>
       <c r="H6" t="n">
-        <v>530</v>
+        <v>460</v>
       </c>
       <c r="I6" t="n">
-        <v>522</v>
+        <v>504</v>
       </c>
       <c r="J6" t="n">
-        <v>473</v>
+        <v>479</v>
       </c>
       <c r="K6" t="n">
-        <v>440</v>
+        <v>466</v>
       </c>
       <c r="L6" t="n">
-        <v>477.5</v>
+        <v>466.4</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>412</v>
+        <v>443</v>
       </c>
       <c r="C7" t="n">
-        <v>480</v>
+        <v>393</v>
       </c>
       <c r="D7" t="n">
-        <v>442</v>
+        <v>431</v>
       </c>
       <c r="E7" t="n">
-        <v>454</v>
+        <v>405</v>
       </c>
       <c r="F7" t="n">
-        <v>486</v>
+        <v>479</v>
       </c>
       <c r="G7" t="n">
-        <v>466</v>
+        <v>422</v>
       </c>
       <c r="H7" t="n">
-        <v>456</v>
+        <v>439</v>
       </c>
       <c r="I7" t="n">
-        <v>455</v>
+        <v>430</v>
       </c>
       <c r="J7" t="n">
-        <v>464</v>
+        <v>475</v>
       </c>
       <c r="K7" t="n">
-        <v>443</v>
+        <v>399</v>
       </c>
       <c r="L7" t="n">
-        <v>455.8</v>
+        <v>431.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>501</v>
+        <v>481</v>
       </c>
       <c r="C8" t="n">
-        <v>498</v>
+        <v>491</v>
       </c>
       <c r="D8" t="n">
-        <v>562</v>
+        <v>479</v>
       </c>
       <c r="E8" t="n">
-        <v>559</v>
+        <v>437</v>
       </c>
       <c r="F8" t="n">
-        <v>473</v>
+        <v>481</v>
       </c>
       <c r="G8" t="n">
-        <v>549</v>
+        <v>448</v>
       </c>
       <c r="H8" t="n">
-        <v>453</v>
+        <v>467</v>
       </c>
       <c r="I8" t="n">
-        <v>474</v>
+        <v>520</v>
       </c>
       <c r="J8" t="n">
-        <v>478</v>
+        <v>533</v>
       </c>
       <c r="K8" t="n">
-        <v>447</v>
+        <v>512</v>
       </c>
       <c r="L8" t="n">
-        <v>499.4</v>
+        <v>484.9</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>489</v>
+        <v>469</v>
       </c>
       <c r="C9" t="n">
-        <v>418</v>
+        <v>495</v>
       </c>
       <c r="D9" t="n">
-        <v>447</v>
+        <v>483</v>
       </c>
       <c r="E9" t="n">
-        <v>468</v>
+        <v>454</v>
       </c>
       <c r="F9" t="n">
-        <v>434</v>
+        <v>486</v>
       </c>
       <c r="G9" t="n">
-        <v>450</v>
+        <v>395</v>
       </c>
       <c r="H9" t="n">
-        <v>468</v>
+        <v>532</v>
       </c>
       <c r="I9" t="n">
-        <v>452</v>
+        <v>465</v>
       </c>
       <c r="J9" t="n">
-        <v>455</v>
+        <v>515</v>
       </c>
       <c r="K9" t="n">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="L9" t="n">
-        <v>454.1</v>
+        <v>476.6</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="C10" t="n">
-        <v>539</v>
+        <v>462</v>
       </c>
       <c r="D10" t="n">
-        <v>523</v>
+        <v>542</v>
       </c>
       <c r="E10" t="n">
-        <v>526</v>
+        <v>485</v>
       </c>
       <c r="F10" t="n">
-        <v>431</v>
+        <v>541</v>
       </c>
       <c r="G10" t="n">
-        <v>508</v>
+        <v>455</v>
       </c>
       <c r="H10" t="n">
-        <v>543</v>
+        <v>514</v>
       </c>
       <c r="I10" t="n">
-        <v>526</v>
+        <v>531</v>
       </c>
       <c r="J10" t="n">
-        <v>466</v>
+        <v>512</v>
       </c>
       <c r="K10" t="n">
-        <v>498</v>
+        <v>471</v>
       </c>
       <c r="L10" t="n">
-        <v>504.4</v>
+        <v>498.2</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>449</v>
+        <v>406</v>
       </c>
       <c r="C11" t="n">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="D11" t="n">
-        <v>411</v>
+        <v>385</v>
       </c>
       <c r="E11" t="n">
-        <v>403</v>
+        <v>446</v>
       </c>
       <c r="F11" t="n">
-        <v>415</v>
+        <v>371</v>
       </c>
       <c r="G11" t="n">
-        <v>381</v>
+        <v>367</v>
       </c>
       <c r="H11" t="n">
-        <v>425</v>
+        <v>391</v>
       </c>
       <c r="I11" t="n">
-        <v>424</v>
+        <v>399</v>
       </c>
       <c r="J11" t="n">
-        <v>411</v>
+        <v>440</v>
       </c>
       <c r="K11" t="n">
-        <v>403</v>
+        <v>367</v>
       </c>
       <c r="L11" t="n">
-        <v>416</v>
+        <v>401.2</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="C12" t="n">
-        <v>510</v>
+        <v>548</v>
       </c>
       <c r="D12" t="n">
-        <v>562</v>
+        <v>501</v>
       </c>
       <c r="E12" t="n">
-        <v>497</v>
+        <v>524</v>
       </c>
       <c r="F12" t="n">
-        <v>468</v>
+        <v>482</v>
       </c>
       <c r="G12" t="n">
         <v>473</v>
       </c>
       <c r="H12" t="n">
-        <v>529</v>
+        <v>522</v>
       </c>
       <c r="I12" t="n">
-        <v>510</v>
+        <v>470</v>
       </c>
       <c r="J12" t="n">
-        <v>503</v>
+        <v>540</v>
       </c>
       <c r="K12" t="n">
-        <v>549</v>
+        <v>477</v>
       </c>
       <c r="L12" t="n">
-        <v>509</v>
+        <v>502.2</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>511</v>
+        <v>441</v>
       </c>
       <c r="C13" t="n">
-        <v>535</v>
+        <v>464</v>
       </c>
       <c r="D13" t="n">
-        <v>482</v>
+        <v>512</v>
       </c>
       <c r="E13" t="n">
-        <v>517</v>
+        <v>551</v>
       </c>
       <c r="F13" t="n">
-        <v>539</v>
+        <v>512</v>
       </c>
       <c r="G13" t="n">
-        <v>490</v>
+        <v>520</v>
       </c>
       <c r="H13" t="n">
-        <v>524</v>
+        <v>564</v>
       </c>
       <c r="I13" t="n">
-        <v>465</v>
+        <v>547</v>
       </c>
       <c r="J13" t="n">
+        <v>476</v>
+      </c>
+      <c r="K13" t="n">
         <v>495</v>
       </c>
-      <c r="K13" t="n">
-        <v>516</v>
-      </c>
       <c r="L13" t="n">
-        <v>507.4</v>
+        <v>508.2</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>504</v>
+        <v>513</v>
       </c>
       <c r="C14" t="n">
+        <v>506</v>
+      </c>
+      <c r="D14" t="n">
         <v>524</v>
       </c>
-      <c r="D14" t="n">
-        <v>502</v>
-      </c>
       <c r="E14" t="n">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="F14" t="n">
-        <v>517</v>
+        <v>489</v>
       </c>
       <c r="G14" t="n">
-        <v>500</v>
+        <v>540</v>
       </c>
       <c r="H14" t="n">
-        <v>531</v>
+        <v>469</v>
       </c>
       <c r="I14" t="n">
-        <v>499</v>
+        <v>536</v>
       </c>
       <c r="J14" t="n">
-        <v>518</v>
+        <v>494</v>
       </c>
       <c r="K14" t="n">
-        <v>495</v>
+        <v>533</v>
       </c>
       <c r="L14" t="n">
-        <v>508</v>
+        <v>509.1</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>457</v>
+        <v>429</v>
       </c>
       <c r="C15" t="n">
-        <v>457</v>
+        <v>423</v>
       </c>
       <c r="D15" t="n">
-        <v>507</v>
+        <v>449</v>
       </c>
       <c r="E15" t="n">
-        <v>423</v>
+        <v>471</v>
       </c>
       <c r="F15" t="n">
-        <v>472</v>
+        <v>495</v>
       </c>
       <c r="G15" t="n">
-        <v>455</v>
+        <v>410</v>
       </c>
       <c r="H15" t="n">
-        <v>446</v>
+        <v>493</v>
       </c>
       <c r="I15" t="n">
-        <v>447</v>
+        <v>535</v>
       </c>
       <c r="J15" t="n">
-        <v>497</v>
+        <v>426</v>
       </c>
       <c r="K15" t="n">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="L15" t="n">
-        <v>459.3</v>
+        <v>456.6</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>420</v>
+        <v>443</v>
       </c>
       <c r="C16" t="n">
-        <v>471</v>
+        <v>449</v>
       </c>
       <c r="D16" t="n">
-        <v>458</v>
+        <v>407</v>
       </c>
       <c r="E16" t="n">
-        <v>482</v>
+        <v>434</v>
       </c>
       <c r="F16" t="n">
-        <v>480</v>
+        <v>441</v>
       </c>
       <c r="G16" t="n">
-        <v>528</v>
+        <v>450</v>
       </c>
       <c r="H16" t="n">
-        <v>467</v>
+        <v>483</v>
       </c>
       <c r="I16" t="n">
-        <v>503</v>
+        <v>461</v>
       </c>
       <c r="J16" t="n">
-        <v>499</v>
+        <v>464</v>
       </c>
       <c r="K16" t="n">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="L16" t="n">
-        <v>476</v>
+        <v>448.2</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
+        <v>435</v>
+      </c>
+      <c r="C17" t="n">
+        <v>443</v>
+      </c>
+      <c r="D17" t="n">
+        <v>519</v>
+      </c>
+      <c r="E17" t="n">
         <v>530</v>
       </c>
-      <c r="C17" t="n">
-        <v>537</v>
-      </c>
-      <c r="D17" t="n">
-        <v>420</v>
-      </c>
-      <c r="E17" t="n">
-        <v>470</v>
-      </c>
       <c r="F17" t="n">
-        <v>448</v>
+        <v>585</v>
       </c>
       <c r="G17" t="n">
-        <v>408</v>
+        <v>478</v>
       </c>
       <c r="H17" t="n">
-        <v>445</v>
+        <v>486</v>
       </c>
       <c r="I17" t="n">
-        <v>508</v>
+        <v>514</v>
       </c>
       <c r="J17" t="n">
-        <v>492</v>
+        <v>440</v>
       </c>
       <c r="K17" t="n">
-        <v>476</v>
+        <v>506</v>
       </c>
       <c r="L17" t="n">
-        <v>473.4</v>
+        <v>493.6</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
+        <v>548</v>
+      </c>
+      <c r="C18" t="n">
+        <v>559</v>
+      </c>
+      <c r="D18" t="n">
+        <v>609</v>
+      </c>
+      <c r="E18" t="n">
+        <v>527</v>
+      </c>
+      <c r="F18" t="n">
+        <v>550</v>
+      </c>
+      <c r="G18" t="n">
+        <v>524</v>
+      </c>
+      <c r="H18" t="n">
         <v>530</v>
       </c>
-      <c r="C18" t="n">
-        <v>546</v>
-      </c>
-      <c r="D18" t="n">
-        <v>505</v>
-      </c>
-      <c r="E18" t="n">
-        <v>534</v>
-      </c>
-      <c r="F18" t="n">
-        <v>569</v>
-      </c>
-      <c r="G18" t="n">
-        <v>565</v>
-      </c>
-      <c r="H18" t="n">
-        <v>503</v>
-      </c>
       <c r="I18" t="n">
-        <v>564</v>
+        <v>492</v>
       </c>
       <c r="J18" t="n">
-        <v>500</v>
+        <v>673</v>
       </c>
       <c r="K18" t="n">
-        <v>552</v>
+        <v>579</v>
       </c>
       <c r="L18" t="n">
-        <v>536.8</v>
+        <v>559.1</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>562</v>
+        <v>444</v>
       </c>
       <c r="C19" t="n">
-        <v>519</v>
+        <v>577</v>
       </c>
       <c r="D19" t="n">
-        <v>556</v>
+        <v>487</v>
       </c>
       <c r="E19" t="n">
-        <v>460</v>
+        <v>496</v>
       </c>
       <c r="F19" t="n">
-        <v>563</v>
+        <v>463</v>
       </c>
       <c r="G19" t="n">
-        <v>560</v>
+        <v>518</v>
       </c>
       <c r="H19" t="n">
-        <v>575</v>
+        <v>547</v>
       </c>
       <c r="I19" t="n">
-        <v>474</v>
+        <v>462</v>
       </c>
       <c r="J19" t="n">
-        <v>526</v>
+        <v>511</v>
       </c>
       <c r="K19" t="n">
-        <v>474</v>
+        <v>522</v>
       </c>
       <c r="L19" t="n">
-        <v>526.9</v>
+        <v>502.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="C20" t="n">
-        <v>493</v>
+        <v>453</v>
       </c>
       <c r="D20" t="n">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="E20" t="n">
-        <v>552</v>
+        <v>442</v>
       </c>
       <c r="F20" t="n">
-        <v>439</v>
+        <v>522</v>
       </c>
       <c r="G20" t="n">
-        <v>536</v>
+        <v>488</v>
       </c>
       <c r="H20" t="n">
-        <v>498</v>
+        <v>481</v>
       </c>
       <c r="I20" t="n">
-        <v>492</v>
+        <v>519</v>
       </c>
       <c r="J20" t="n">
-        <v>455</v>
+        <v>537</v>
       </c>
       <c r="K20" t="n">
-        <v>486</v>
+        <v>511</v>
       </c>
       <c r="L20" t="n">
-        <v>496.9</v>
+        <v>498.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="C21" t="n">
-        <v>452</v>
+        <v>462</v>
       </c>
       <c r="D21" t="n">
-        <v>496</v>
+        <v>431</v>
       </c>
       <c r="E21" t="n">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="F21" t="n">
-        <v>432</v>
+        <v>522</v>
       </c>
       <c r="G21" t="n">
-        <v>492</v>
+        <v>462</v>
       </c>
       <c r="H21" t="n">
-        <v>463</v>
+        <v>439</v>
       </c>
       <c r="I21" t="n">
+        <v>429</v>
+      </c>
+      <c r="J21" t="n">
         <v>470</v>
       </c>
-      <c r="J21" t="n">
-        <v>483</v>
-      </c>
       <c r="K21" t="n">
-        <v>452</v>
+        <v>531</v>
       </c>
       <c r="L21" t="n">
-        <v>464.9</v>
+        <v>461.9</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>487</v>
+        <v>458</v>
       </c>
       <c r="C22" t="n">
-        <v>499</v>
+        <v>446</v>
       </c>
       <c r="D22" t="n">
-        <v>467</v>
+        <v>534</v>
       </c>
       <c r="E22" t="n">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="F22" t="n">
-        <v>462</v>
+        <v>417</v>
       </c>
       <c r="G22" t="n">
-        <v>495</v>
+        <v>468</v>
       </c>
       <c r="H22" t="n">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="I22" t="n">
-        <v>480</v>
+        <v>486</v>
       </c>
       <c r="J22" t="n">
-        <v>462</v>
+        <v>497</v>
       </c>
       <c r="K22" t="n">
-        <v>439</v>
+        <v>474</v>
       </c>
       <c r="L22" t="n">
-        <v>479.5</v>
+        <v>479.8</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>464</v>
+        <v>456</v>
       </c>
       <c r="C23" t="n">
-        <v>421</v>
+        <v>447</v>
       </c>
       <c r="D23" t="n">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="E23" t="n">
         <v>452</v>
       </c>
       <c r="F23" t="n">
-        <v>433</v>
+        <v>464</v>
       </c>
       <c r="G23" t="n">
-        <v>429</v>
+        <v>474</v>
       </c>
       <c r="H23" t="n">
-        <v>398</v>
+        <v>421</v>
       </c>
       <c r="I23" t="n">
-        <v>436</v>
+        <v>472</v>
       </c>
       <c r="J23" t="n">
-        <v>465</v>
+        <v>393</v>
       </c>
       <c r="K23" t="n">
-        <v>452</v>
+        <v>432</v>
       </c>
       <c r="L23" t="n">
-        <v>441.8</v>
+        <v>448</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>384</v>
+        <v>463</v>
       </c>
       <c r="C24" t="n">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="D24" t="n">
-        <v>455</v>
+        <v>378</v>
       </c>
       <c r="E24" t="n">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="F24" t="n">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="G24" t="n">
-        <v>407</v>
+        <v>395</v>
       </c>
       <c r="H24" t="n">
-        <v>443</v>
+        <v>423</v>
       </c>
       <c r="I24" t="n">
+        <v>492</v>
+      </c>
+      <c r="J24" t="n">
         <v>406</v>
       </c>
-      <c r="J24" t="n">
-        <v>407</v>
-      </c>
       <c r="K24" t="n">
-        <v>441</v>
+        <v>394</v>
       </c>
       <c r="L24" t="n">
-        <v>419.2</v>
+        <v>421.3</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>421</v>
+        <v>395</v>
       </c>
       <c r="C25" t="n">
-        <v>416</v>
+        <v>466</v>
       </c>
       <c r="D25" t="n">
-        <v>416</v>
+        <v>367</v>
       </c>
       <c r="E25" t="n">
-        <v>417</v>
+        <v>391</v>
       </c>
       <c r="F25" t="n">
-        <v>417</v>
+        <v>383</v>
       </c>
       <c r="G25" t="n">
-        <v>431</v>
+        <v>439</v>
       </c>
       <c r="H25" t="n">
-        <v>404</v>
+        <v>425</v>
       </c>
       <c r="I25" t="n">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="J25" t="n">
-        <v>459</v>
+        <v>418</v>
       </c>
       <c r="K25" t="n">
-        <v>377</v>
+        <v>463</v>
       </c>
       <c r="L25" t="n">
-        <v>413.1</v>
+        <v>415.7</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>492</v>
+        <v>623</v>
       </c>
       <c r="C26" t="n">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="D26" t="n">
-        <v>471</v>
+        <v>580</v>
       </c>
       <c r="E26" t="n">
+        <v>463</v>
+      </c>
+      <c r="F26" t="n">
+        <v>545</v>
+      </c>
+      <c r="G26" t="n">
+        <v>650</v>
+      </c>
+      <c r="H26" t="n">
+        <v>601</v>
+      </c>
+      <c r="I26" t="n">
+        <v>477</v>
+      </c>
+      <c r="J26" t="n">
+        <v>592</v>
+      </c>
+      <c r="K26" t="n">
         <v>590</v>
       </c>
-      <c r="F26" t="n">
-        <v>515</v>
-      </c>
-      <c r="G26" t="n">
-        <v>607</v>
-      </c>
-      <c r="H26" t="n">
-        <v>598</v>
-      </c>
-      <c r="I26" t="n">
-        <v>577</v>
-      </c>
-      <c r="J26" t="n">
-        <v>535</v>
-      </c>
-      <c r="K26" t="n">
-        <v>612</v>
-      </c>
       <c r="L26" t="n">
-        <v>551</v>
+        <v>561.2</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="C27" t="n">
-        <v>441</v>
+        <v>461</v>
       </c>
       <c r="D27" t="n">
-        <v>448</v>
+        <v>418</v>
       </c>
       <c r="E27" t="n">
-        <v>476</v>
+        <v>415</v>
       </c>
       <c r="F27" t="n">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="G27" t="n">
-        <v>448</v>
+        <v>440</v>
       </c>
       <c r="H27" t="n">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="I27" t="n">
-        <v>408</v>
+        <v>424</v>
       </c>
       <c r="J27" t="n">
+        <v>438</v>
+      </c>
+      <c r="K27" t="n">
         <v>450</v>
       </c>
-      <c r="K27" t="n">
-        <v>438</v>
-      </c>
       <c r="L27" t="n">
-        <v>440.5</v>
+        <v>436.3</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
+        <v>492</v>
+      </c>
+      <c r="C28" t="n">
+        <v>488</v>
+      </c>
+      <c r="D28" t="n">
+        <v>500</v>
+      </c>
+      <c r="E28" t="n">
+        <v>452</v>
+      </c>
+      <c r="F28" t="n">
+        <v>454</v>
+      </c>
+      <c r="G28" t="n">
+        <v>467</v>
+      </c>
+      <c r="H28" t="n">
+        <v>482</v>
+      </c>
+      <c r="I28" t="n">
+        <v>468</v>
+      </c>
+      <c r="J28" t="n">
+        <v>453</v>
+      </c>
+      <c r="K28" t="n">
         <v>484</v>
       </c>
-      <c r="C28" t="n">
-        <v>468</v>
-      </c>
-      <c r="D28" t="n">
-        <v>482</v>
-      </c>
-      <c r="E28" t="n">
-        <v>457</v>
-      </c>
-      <c r="F28" t="n">
-        <v>441</v>
-      </c>
-      <c r="G28" t="n">
-        <v>459</v>
-      </c>
-      <c r="H28" t="n">
-        <v>454</v>
-      </c>
-      <c r="I28" t="n">
-        <v>458</v>
-      </c>
-      <c r="J28" t="n">
+      <c r="L28" t="n">
         <v>474</v>
-      </c>
-      <c r="K28" t="n">
-        <v>451</v>
-      </c>
-      <c r="L28" t="n">
-        <v>462.8</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>475</v>
+        <v>413</v>
       </c>
       <c r="C29" t="n">
-        <v>555</v>
+        <v>405</v>
       </c>
       <c r="D29" t="n">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="E29" t="n">
-        <v>461</v>
+        <v>468</v>
       </c>
       <c r="F29" t="n">
-        <v>436</v>
+        <v>484</v>
       </c>
       <c r="G29" t="n">
-        <v>479</v>
+        <v>494</v>
       </c>
       <c r="H29" t="n">
-        <v>479</v>
+        <v>423</v>
       </c>
       <c r="I29" t="n">
-        <v>431</v>
+        <v>457</v>
       </c>
       <c r="J29" t="n">
-        <v>484</v>
+        <v>392</v>
       </c>
       <c r="K29" t="n">
-        <v>425</v>
+        <v>447</v>
       </c>
       <c r="L29" t="n">
-        <v>466.7</v>
+        <v>441.5</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>425</v>
+        <v>395</v>
       </c>
       <c r="C30" t="n">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D30" t="n">
-        <v>386</v>
+        <v>475</v>
       </c>
       <c r="E30" t="n">
-        <v>402</v>
+        <v>507</v>
       </c>
       <c r="F30" t="n">
-        <v>463</v>
+        <v>419</v>
       </c>
       <c r="G30" t="n">
-        <v>483</v>
+        <v>420</v>
       </c>
       <c r="H30" t="n">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="I30" t="n">
-        <v>447</v>
+        <v>480</v>
       </c>
       <c r="J30" t="n">
-        <v>448</v>
+        <v>482</v>
       </c>
       <c r="K30" t="n">
-        <v>453</v>
+        <v>418</v>
       </c>
       <c r="L30" t="n">
-        <v>437.5</v>
+        <v>447.5</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>527</v>
+        <v>414</v>
       </c>
       <c r="C31" t="n">
         <v>491</v>
       </c>
       <c r="D31" t="n">
-        <v>446</v>
+        <v>404</v>
       </c>
       <c r="E31" t="n">
-        <v>448</v>
+        <v>435</v>
       </c>
       <c r="F31" t="n">
-        <v>491</v>
+        <v>430</v>
       </c>
       <c r="G31" t="n">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="H31" t="n">
-        <v>412</v>
+        <v>434</v>
       </c>
       <c r="I31" t="n">
-        <v>471</v>
+        <v>450</v>
       </c>
       <c r="J31" t="n">
-        <v>432</v>
+        <v>437</v>
       </c>
       <c r="K31" t="n">
-        <v>425</v>
+        <v>485</v>
       </c>
       <c r="L31" t="n">
-        <v>457.4</v>
+        <v>440.9</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="C32" t="n">
-        <v>394</v>
+        <v>481</v>
       </c>
       <c r="D32" t="n">
-        <v>397</v>
+        <v>419</v>
       </c>
       <c r="E32" t="n">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="F32" t="n">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="G32" t="n">
-        <v>419</v>
+        <v>391</v>
       </c>
       <c r="H32" t="n">
-        <v>378</v>
+        <v>411</v>
       </c>
       <c r="I32" t="n">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="J32" t="n">
-        <v>462</v>
+        <v>440</v>
       </c>
       <c r="K32" t="n">
-        <v>430</v>
+        <v>396</v>
       </c>
       <c r="L32" t="n">
-        <v>414.3</v>
+        <v>418</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>400</v>
+        <v>430</v>
       </c>
       <c r="C33" t="n">
-        <v>383</v>
+        <v>456</v>
       </c>
       <c r="D33" t="n">
-        <v>423</v>
+        <v>456</v>
       </c>
       <c r="E33" t="n">
-        <v>380</v>
+        <v>439</v>
       </c>
       <c r="F33" t="n">
-        <v>395</v>
+        <v>455</v>
       </c>
       <c r="G33" t="n">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="H33" t="n">
-        <v>423</v>
+        <v>452</v>
       </c>
       <c r="I33" t="n">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="J33" t="n">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="K33" t="n">
-        <v>415</v>
+        <v>443</v>
       </c>
       <c r="L33" t="n">
-        <v>403.7</v>
+        <v>436.5</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>397</v>
+        <v>440</v>
       </c>
       <c r="C34" t="n">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="D34" t="n">
-        <v>399</v>
+        <v>520</v>
       </c>
       <c r="E34" t="n">
-        <v>488</v>
+        <v>453</v>
       </c>
       <c r="F34" t="n">
-        <v>441</v>
+        <v>420</v>
       </c>
       <c r="G34" t="n">
-        <v>428</v>
+        <v>435</v>
       </c>
       <c r="H34" t="n">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="I34" t="n">
-        <v>442</v>
+        <v>422</v>
       </c>
       <c r="J34" t="n">
-        <v>399</v>
+        <v>412</v>
       </c>
       <c r="K34" t="n">
-        <v>499</v>
+        <v>411</v>
       </c>
       <c r="L34" t="n">
-        <v>430.6</v>
+        <v>432.8</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
+        <v>493</v>
+      </c>
+      <c r="C35" t="n">
+        <v>462</v>
+      </c>
+      <c r="D35" t="n">
+        <v>488</v>
+      </c>
+      <c r="E35" t="n">
+        <v>465</v>
+      </c>
+      <c r="F35" t="n">
+        <v>448</v>
+      </c>
+      <c r="G35" t="n">
+        <v>474</v>
+      </c>
+      <c r="H35" t="n">
         <v>492</v>
       </c>
-      <c r="C35" t="n">
-        <v>501</v>
-      </c>
-      <c r="D35" t="n">
-        <v>477</v>
-      </c>
-      <c r="E35" t="n">
-        <v>456</v>
-      </c>
-      <c r="F35" t="n">
-        <v>457</v>
-      </c>
-      <c r="G35" t="n">
-        <v>458</v>
-      </c>
-      <c r="H35" t="n">
-        <v>541</v>
-      </c>
       <c r="I35" t="n">
-        <v>439</v>
+        <v>480</v>
       </c>
       <c r="J35" t="n">
-        <v>488</v>
+        <v>464</v>
       </c>
       <c r="K35" t="n">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="L35" t="n">
-        <v>474.8</v>
+        <v>469.5</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>404</v>
+        <v>385</v>
       </c>
       <c r="C36" t="n">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D36" t="n">
-        <v>391</v>
+        <v>364</v>
       </c>
       <c r="E36" t="n">
-        <v>357</v>
+        <v>398</v>
       </c>
       <c r="F36" t="n">
-        <v>368</v>
+        <v>441</v>
       </c>
       <c r="G36" t="n">
-        <v>376</v>
+        <v>423</v>
       </c>
       <c r="H36" t="n">
-        <v>368</v>
+        <v>428</v>
       </c>
       <c r="I36" t="n">
-        <v>384</v>
+        <v>422</v>
       </c>
       <c r="J36" t="n">
-        <v>378</v>
+        <v>416</v>
       </c>
       <c r="K36" t="n">
-        <v>367</v>
+        <v>415</v>
       </c>
       <c r="L36" t="n">
-        <v>378.6</v>
+        <v>407.9</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>488</v>
+        <v>418</v>
       </c>
       <c r="C37" t="n">
-        <v>412</v>
+        <v>474</v>
       </c>
       <c r="D37" t="n">
-        <v>454</v>
+        <v>419</v>
       </c>
       <c r="E37" t="n">
-        <v>494</v>
+        <v>466</v>
       </c>
       <c r="F37" t="n">
-        <v>474</v>
+        <v>402</v>
       </c>
       <c r="G37" t="n">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="H37" t="n">
-        <v>457</v>
+        <v>436</v>
       </c>
       <c r="I37" t="n">
-        <v>419</v>
+        <v>443</v>
       </c>
       <c r="J37" t="n">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="K37" t="n">
-        <v>460</v>
+        <v>418</v>
       </c>
       <c r="L37" t="n">
-        <v>463.7</v>
+        <v>447</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>494</v>
+        <v>545</v>
       </c>
       <c r="C38" t="n">
-        <v>448</v>
+        <v>502</v>
       </c>
       <c r="D38" t="n">
-        <v>525</v>
+        <v>506</v>
       </c>
       <c r="E38" t="n">
-        <v>521</v>
+        <v>579</v>
       </c>
       <c r="F38" t="n">
-        <v>549</v>
+        <v>579</v>
       </c>
       <c r="G38" t="n">
-        <v>454</v>
+        <v>522</v>
       </c>
       <c r="H38" t="n">
-        <v>453</v>
+        <v>534</v>
       </c>
       <c r="I38" t="n">
-        <v>436</v>
+        <v>558</v>
       </c>
       <c r="J38" t="n">
-        <v>600</v>
+        <v>439</v>
       </c>
       <c r="K38" t="n">
-        <v>574</v>
+        <v>509</v>
       </c>
       <c r="L38" t="n">
-        <v>505.4</v>
+        <v>527.3</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>401</v>
+        <v>414</v>
       </c>
       <c r="C39" t="n">
-        <v>401</v>
+        <v>439</v>
       </c>
       <c r="D39" t="n">
-        <v>376</v>
+        <v>383</v>
       </c>
       <c r="E39" t="n">
         <v>430</v>
       </c>
       <c r="F39" t="n">
-        <v>399</v>
+        <v>378</v>
       </c>
       <c r="G39" t="n">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="H39" t="n">
-        <v>455</v>
+        <v>401</v>
       </c>
       <c r="I39" t="n">
-        <v>506</v>
+        <v>442</v>
       </c>
       <c r="J39" t="n">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="K39" t="n">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="L39" t="n">
-        <v>415.2</v>
+        <v>412.8</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>473</v>
+        <v>389</v>
       </c>
       <c r="C40" t="n">
-        <v>420</v>
+        <v>403</v>
       </c>
       <c r="D40" t="n">
-        <v>404</v>
+        <v>465</v>
       </c>
       <c r="E40" t="n">
-        <v>453</v>
+        <v>480</v>
       </c>
       <c r="F40" t="n">
-        <v>440</v>
+        <v>513</v>
       </c>
       <c r="G40" t="n">
-        <v>476</v>
+        <v>428</v>
       </c>
       <c r="H40" t="n">
-        <v>453</v>
+        <v>430</v>
       </c>
       <c r="I40" t="n">
-        <v>469</v>
+        <v>461</v>
       </c>
       <c r="J40" t="n">
-        <v>429</v>
+        <v>481</v>
       </c>
       <c r="K40" t="n">
-        <v>409</v>
+        <v>437</v>
       </c>
       <c r="L40" t="n">
-        <v>442.6</v>
+        <v>448.7</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>474</v>
+        <v>438</v>
       </c>
       <c r="C41" t="n">
-        <v>470</v>
+        <v>488</v>
       </c>
       <c r="D41" t="n">
-        <v>498</v>
+        <v>461</v>
       </c>
       <c r="E41" t="n">
-        <v>515</v>
+        <v>479</v>
       </c>
       <c r="F41" t="n">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="G41" t="n">
-        <v>444</v>
+        <v>499</v>
       </c>
       <c r="H41" t="n">
-        <v>547</v>
+        <v>475</v>
       </c>
       <c r="I41" t="n">
-        <v>493</v>
+        <v>466</v>
       </c>
       <c r="J41" t="n">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="K41" t="n">
-        <v>435</v>
+        <v>517</v>
       </c>
       <c r="L41" t="n">
-        <v>490.1</v>
+        <v>483.5</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>477</v>
+        <v>489</v>
       </c>
       <c r="C42" t="n">
-        <v>436</v>
+        <v>483</v>
       </c>
       <c r="D42" t="n">
-        <v>479</v>
+        <v>446</v>
       </c>
       <c r="E42" t="n">
-        <v>493</v>
+        <v>473</v>
       </c>
       <c r="F42" t="n">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c r="G42" t="n">
-        <v>477</v>
+        <v>454</v>
       </c>
       <c r="H42" t="n">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="I42" t="n">
-        <v>453</v>
+        <v>437</v>
       </c>
       <c r="J42" t="n">
-        <v>472</v>
+        <v>456</v>
       </c>
       <c r="K42" t="n">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L42" t="n">
-        <v>463.8</v>
+        <v>461</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C43" t="n">
-        <v>456</v>
+        <v>548</v>
       </c>
       <c r="D43" t="n">
-        <v>468</v>
+        <v>520</v>
       </c>
       <c r="E43" t="n">
-        <v>436</v>
+        <v>491</v>
       </c>
       <c r="F43" t="n">
         <v>487</v>
       </c>
       <c r="G43" t="n">
-        <v>492</v>
+        <v>458</v>
       </c>
       <c r="H43" t="n">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="I43" t="n">
-        <v>496</v>
+        <v>456</v>
       </c>
       <c r="J43" t="n">
-        <v>472</v>
+        <v>509</v>
       </c>
       <c r="K43" t="n">
-        <v>440</v>
+        <v>456</v>
       </c>
       <c r="L43" t="n">
-        <v>473.1</v>
+        <v>491.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>444</v>
+        <v>494</v>
       </c>
       <c r="C44" t="n">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D44" t="n">
-        <v>472</v>
+        <v>453</v>
       </c>
       <c r="E44" t="n">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="F44" t="n">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="G44" t="n">
-        <v>472</v>
+        <v>457</v>
       </c>
       <c r="H44" t="n">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="I44" t="n">
-        <v>405</v>
+        <v>453</v>
       </c>
       <c r="J44" t="n">
-        <v>450</v>
+        <v>436</v>
       </c>
       <c r="K44" t="n">
-        <v>448</v>
+        <v>433</v>
       </c>
       <c r="L44" t="n">
-        <v>452.6</v>
+        <v>455.2</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>442</v>
+        <v>513</v>
       </c>
       <c r="C45" t="n">
-        <v>475</v>
+        <v>543</v>
       </c>
       <c r="D45" t="n">
-        <v>469</v>
+        <v>506</v>
       </c>
       <c r="E45" t="n">
-        <v>438</v>
+        <v>447</v>
       </c>
       <c r="F45" t="n">
-        <v>430</v>
+        <v>479</v>
       </c>
       <c r="G45" t="n">
-        <v>496</v>
+        <v>434</v>
       </c>
       <c r="H45" t="n">
-        <v>507</v>
+        <v>458</v>
       </c>
       <c r="I45" t="n">
-        <v>474</v>
+        <v>493</v>
       </c>
       <c r="J45" t="n">
-        <v>489</v>
+        <v>443</v>
       </c>
       <c r="K45" t="n">
-        <v>519</v>
+        <v>491</v>
       </c>
       <c r="L45" t="n">
-        <v>473.9</v>
+        <v>480.7</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>365</v>
+        <v>411</v>
       </c>
       <c r="C46" t="n">
+        <v>371</v>
+      </c>
+      <c r="D46" t="n">
+        <v>368</v>
+      </c>
+      <c r="E46" t="n">
+        <v>371</v>
+      </c>
+      <c r="F46" t="n">
+        <v>435</v>
+      </c>
+      <c r="G46" t="n">
+        <v>444</v>
+      </c>
+      <c r="H46" t="n">
+        <v>387</v>
+      </c>
+      <c r="I46" t="n">
         <v>374</v>
       </c>
-      <c r="D46" t="n">
-        <v>422</v>
-      </c>
-      <c r="E46" t="n">
-        <v>453</v>
-      </c>
-      <c r="F46" t="n">
-        <v>374</v>
-      </c>
-      <c r="G46" t="n">
-        <v>368</v>
-      </c>
-      <c r="H46" t="n">
-        <v>384</v>
-      </c>
-      <c r="I46" t="n">
-        <v>429</v>
-      </c>
       <c r="J46" t="n">
-        <v>381</v>
+        <v>456</v>
       </c>
       <c r="K46" t="n">
-        <v>378</v>
+        <v>439</v>
       </c>
       <c r="L46" t="n">
-        <v>392.8</v>
+        <v>405.6</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>448</v>
+        <v>532</v>
       </c>
       <c r="C47" t="n">
-        <v>567</v>
+        <v>604</v>
       </c>
       <c r="D47" t="n">
-        <v>441</v>
+        <v>487</v>
       </c>
       <c r="E47" t="n">
-        <v>556</v>
+        <v>452</v>
       </c>
       <c r="F47" t="n">
-        <v>542</v>
+        <v>558</v>
       </c>
       <c r="G47" t="n">
-        <v>626</v>
+        <v>530</v>
       </c>
       <c r="H47" t="n">
-        <v>465</v>
+        <v>570</v>
       </c>
       <c r="I47" t="n">
         <v>506</v>
       </c>
       <c r="J47" t="n">
-        <v>477</v>
+        <v>498</v>
       </c>
       <c r="K47" t="n">
-        <v>589</v>
+        <v>508</v>
       </c>
       <c r="L47" t="n">
-        <v>521.7</v>
+        <v>524.5</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>475</v>
+        <v>562</v>
       </c>
       <c r="C48" t="n">
+        <v>510</v>
+      </c>
+      <c r="D48" t="n">
+        <v>459</v>
+      </c>
+      <c r="E48" t="n">
+        <v>507</v>
+      </c>
+      <c r="F48" t="n">
+        <v>514</v>
+      </c>
+      <c r="G48" t="n">
+        <v>457</v>
+      </c>
+      <c r="H48" t="n">
+        <v>485</v>
+      </c>
+      <c r="I48" t="n">
         <v>527</v>
       </c>
-      <c r="D48" t="n">
-        <v>544</v>
-      </c>
-      <c r="E48" t="n">
-        <v>451</v>
-      </c>
-      <c r="F48" t="n">
-        <v>523</v>
-      </c>
-      <c r="G48" t="n">
-        <v>471</v>
-      </c>
-      <c r="H48" t="n">
-        <v>559</v>
-      </c>
-      <c r="I48" t="n">
-        <v>520</v>
-      </c>
       <c r="J48" t="n">
-        <v>471</v>
+        <v>517</v>
       </c>
       <c r="K48" t="n">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="L48" t="n">
-        <v>506.1</v>
+        <v>505.4</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>431</v>
+        <v>463</v>
       </c>
       <c r="C49" t="n">
-        <v>425</v>
+        <v>474</v>
       </c>
       <c r="D49" t="n">
-        <v>449</v>
+        <v>470</v>
       </c>
       <c r="E49" t="n">
-        <v>482</v>
+        <v>444</v>
       </c>
       <c r="F49" t="n">
-        <v>445</v>
+        <v>478</v>
       </c>
       <c r="G49" t="n">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="H49" t="n">
-        <v>462</v>
+        <v>422</v>
       </c>
       <c r="I49" t="n">
-        <v>489</v>
+        <v>416</v>
       </c>
       <c r="J49" t="n">
-        <v>517</v>
+        <v>440</v>
       </c>
       <c r="K49" t="n">
-        <v>480</v>
+        <v>442</v>
       </c>
       <c r="L49" t="n">
-        <v>461.9</v>
+        <v>448.5</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>446</v>
+        <v>424</v>
       </c>
       <c r="C50" t="n">
-        <v>433</v>
+        <v>470</v>
       </c>
       <c r="D50" t="n">
-        <v>411</v>
+        <v>450</v>
       </c>
       <c r="E50" t="n">
-        <v>399</v>
+        <v>413</v>
       </c>
       <c r="F50" t="n">
-        <v>427</v>
+        <v>498</v>
       </c>
       <c r="G50" t="n">
-        <v>407</v>
+        <v>449</v>
       </c>
       <c r="H50" t="n">
-        <v>461</v>
+        <v>414</v>
       </c>
       <c r="I50" t="n">
-        <v>433</v>
+        <v>450</v>
       </c>
       <c r="J50" t="n">
-        <v>410</v>
+        <v>444</v>
       </c>
       <c r="K50" t="n">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="L50" t="n">
-        <v>425.8</v>
+        <v>445.5</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>390</v>
+        <v>405</v>
       </c>
       <c r="C51" t="n">
+        <v>379</v>
+      </c>
+      <c r="D51" t="n">
         <v>376</v>
       </c>
-      <c r="D51" t="n">
-        <v>427</v>
-      </c>
       <c r="E51" t="n">
-        <v>445</v>
+        <v>431</v>
       </c>
       <c r="F51" t="n">
-        <v>468</v>
+        <v>440</v>
       </c>
       <c r="G51" t="n">
-        <v>465</v>
+        <v>435</v>
       </c>
       <c r="H51" t="n">
-        <v>431</v>
+        <v>467</v>
       </c>
       <c r="I51" t="n">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="J51" t="n">
-        <v>446</v>
+        <v>420</v>
       </c>
       <c r="K51" t="n">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="L51" t="n">
-        <v>436.3</v>
+        <v>427.7</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>462.92</v>
+        <v>461.1</v>
       </c>
       <c r="C52" t="n">
-        <v>464.82</v>
+        <v>472.14</v>
       </c>
       <c r="D52" t="n">
-        <v>461.84</v>
+        <v>464.72</v>
       </c>
       <c r="E52" t="n">
-        <v>467.42</v>
+        <v>465</v>
       </c>
       <c r="F52" t="n">
-        <v>463.18</v>
+        <v>472</v>
       </c>
       <c r="G52" t="n">
-        <v>469.72</v>
+        <v>460.58</v>
       </c>
       <c r="H52" t="n">
-        <v>470.3</v>
+        <v>470.12</v>
       </c>
       <c r="I52" t="n">
-        <v>465.86</v>
+        <v>470</v>
       </c>
       <c r="J52" t="n">
-        <v>465.54</v>
+        <v>472.28</v>
       </c>
       <c r="K52" t="n">
-        <v>463.88</v>
+        <v>467.32</v>
       </c>
       <c r="L52" t="n">
-        <v>465.5479999999999</v>
+        <v>467.526</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>2.381304979324341</v>
+        <v>2.323208332061768</v>
       </c>
       <c r="C2" t="n">
-        <v>2.307972192764282</v>
+        <v>2.187607049942017</v>
       </c>
       <c r="D2" t="n">
-        <v>2.483555316925049</v>
+        <v>2.257006168365479</v>
       </c>
       <c r="E2" t="n">
-        <v>2.200762271881104</v>
+        <v>2.283148288726807</v>
       </c>
       <c r="F2" t="n">
-        <v>2.354859352111816</v>
+        <v>2.126490354537964</v>
       </c>
       <c r="G2" t="n">
-        <v>2.185651302337646</v>
+        <v>2.325350284576416</v>
       </c>
       <c r="H2" t="n">
-        <v>2.291225671768188</v>
+        <v>2.368352174758911</v>
       </c>
       <c r="I2" t="n">
-        <v>2.548411130905151</v>
+        <v>2.29983115196228</v>
       </c>
       <c r="J2" t="n">
-        <v>2.423219203948975</v>
+        <v>2.444564342498779</v>
       </c>
       <c r="K2" t="n">
-        <v>2.509812593460083</v>
+        <v>2.43011474609375</v>
       </c>
       <c r="L2" t="n">
-        <v>2.368677401542663</v>
+        <v>2.304567289352417</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>2.280531167984009</v>
+        <v>2.3583083152771</v>
       </c>
       <c r="C3" t="n">
-        <v>2.426852941513062</v>
+        <v>2.407893896102905</v>
       </c>
       <c r="D3" t="n">
-        <v>2.608538627624512</v>
+        <v>2.546190500259399</v>
       </c>
       <c r="E3" t="n">
-        <v>2.989578247070312</v>
+        <v>2.599881410598755</v>
       </c>
       <c r="F3" t="n">
-        <v>2.335538387298584</v>
+        <v>2.230314254760742</v>
       </c>
       <c r="G3" t="n">
-        <v>2.465226650238037</v>
+        <v>2.568794727325439</v>
       </c>
       <c r="H3" t="n">
-        <v>2.345392227172852</v>
+        <v>2.918065071105957</v>
       </c>
       <c r="I3" t="n">
-        <v>2.443603038787842</v>
+        <v>2.390018701553345</v>
       </c>
       <c r="J3" t="n">
-        <v>2.244739294052124</v>
+        <v>2.66196346282959</v>
       </c>
       <c r="K3" t="n">
-        <v>2.175151348114014</v>
+        <v>2.404330492019653</v>
       </c>
       <c r="L3" t="n">
-        <v>2.431515192985535</v>
+        <v>2.508576083183288</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>2.661774873733521</v>
+        <v>2.468752384185791</v>
       </c>
       <c r="C4" t="n">
-        <v>2.537654638290405</v>
+        <v>2.569827318191528</v>
       </c>
       <c r="D4" t="n">
-        <v>2.621079444885254</v>
+        <v>2.439457416534424</v>
       </c>
       <c r="E4" t="n">
-        <v>2.466569185256958</v>
+        <v>2.406373262405396</v>
       </c>
       <c r="F4" t="n">
-        <v>2.490219354629517</v>
+        <v>2.794241428375244</v>
       </c>
       <c r="G4" t="n">
-        <v>2.65807032585144</v>
+        <v>2.588751077651978</v>
       </c>
       <c r="H4" t="n">
-        <v>2.580275535583496</v>
+        <v>2.477309465408325</v>
       </c>
       <c r="I4" t="n">
-        <v>2.53914999961853</v>
+        <v>2.460241079330444</v>
       </c>
       <c r="J4" t="n">
-        <v>2.359540700912476</v>
+        <v>2.420999050140381</v>
       </c>
       <c r="K4" t="n">
-        <v>2.351488828659058</v>
+        <v>2.52606725692749</v>
       </c>
       <c r="L4" t="n">
-        <v>2.526582288742065</v>
+        <v>2.5152019739151</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>2.159833192825317</v>
+        <v>2.160222291946411</v>
       </c>
       <c r="C5" t="n">
-        <v>2.217111825942993</v>
+        <v>2.332405090332031</v>
       </c>
       <c r="D5" t="n">
-        <v>2.144906044006348</v>
+        <v>2.369197130203247</v>
       </c>
       <c r="E5" t="n">
-        <v>2.181143522262573</v>
+        <v>2.288583040237427</v>
       </c>
       <c r="F5" t="n">
-        <v>2.228868246078491</v>
+        <v>2.106853723526001</v>
       </c>
       <c r="G5" t="n">
-        <v>2.186476469039917</v>
+        <v>2.199050903320312</v>
       </c>
       <c r="H5" t="n">
-        <v>2.355155467987061</v>
+        <v>2.262354135513306</v>
       </c>
       <c r="I5" t="n">
-        <v>2.099508762359619</v>
+        <v>2.268895387649536</v>
       </c>
       <c r="J5" t="n">
-        <v>2.095366239547729</v>
+        <v>2.326494932174683</v>
       </c>
       <c r="K5" t="n">
-        <v>2.218429088592529</v>
+        <v>2.251369476318359</v>
       </c>
       <c r="L5" t="n">
-        <v>2.188679885864258</v>
+        <v>2.256542611122131</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>2.152803182601929</v>
+        <v>2.052752017974854</v>
       </c>
       <c r="C6" t="n">
-        <v>1.982284307479858</v>
+        <v>2.646157026290894</v>
       </c>
       <c r="D6" t="n">
-        <v>1.936408758163452</v>
+        <v>2.174335241317749</v>
       </c>
       <c r="E6" t="n">
-        <v>2.317072629928589</v>
+        <v>2.218110322952271</v>
       </c>
       <c r="F6" t="n">
-        <v>1.922613620758057</v>
+        <v>1.96697735786438</v>
       </c>
       <c r="G6" t="n">
-        <v>2.09272027015686</v>
+        <v>2.015248537063599</v>
       </c>
       <c r="H6" t="n">
-        <v>2.343535423278809</v>
+        <v>2.030434608459473</v>
       </c>
       <c r="I6" t="n">
-        <v>2.351219177246094</v>
+        <v>2.273094177246094</v>
       </c>
       <c r="J6" t="n">
-        <v>1.967148542404175</v>
+        <v>2.359652280807495</v>
       </c>
       <c r="K6" t="n">
-        <v>1.918816328048706</v>
+        <v>2.292497634887695</v>
       </c>
       <c r="L6" t="n">
-        <v>2.098462224006653</v>
+        <v>2.20292592048645</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>2.340830564498901</v>
+        <v>2.583260774612427</v>
       </c>
       <c r="C7" t="n">
-        <v>2.410926103591919</v>
+        <v>2.427666187286377</v>
       </c>
       <c r="D7" t="n">
-        <v>2.395698308944702</v>
+        <v>2.47240424156189</v>
       </c>
       <c r="E7" t="n">
-        <v>2.521128416061401</v>
+        <v>2.382408857345581</v>
       </c>
       <c r="F7" t="n">
-        <v>2.371013402938843</v>
+        <v>2.558333873748779</v>
       </c>
       <c r="G7" t="n">
-        <v>2.451867341995239</v>
+        <v>2.510879039764404</v>
       </c>
       <c r="H7" t="n">
-        <v>2.346412897109985</v>
+        <v>2.38111138343811</v>
       </c>
       <c r="I7" t="n">
-        <v>2.396663427352905</v>
+        <v>2.564384937286377</v>
       </c>
       <c r="J7" t="n">
-        <v>2.241727828979492</v>
+        <v>2.810147762298584</v>
       </c>
       <c r="K7" t="n">
-        <v>2.345694541931152</v>
+        <v>2.467469215393066</v>
       </c>
       <c r="L7" t="n">
-        <v>2.382196283340454</v>
+        <v>2.51580662727356</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>2.570608139038086</v>
+        <v>2.386763334274292</v>
       </c>
       <c r="C8" t="n">
-        <v>2.497943162918091</v>
+        <v>2.477324247360229</v>
       </c>
       <c r="D8" t="n">
-        <v>2.353895902633667</v>
+        <v>2.352457523345947</v>
       </c>
       <c r="E8" t="n">
-        <v>2.385960817337036</v>
+        <v>2.392643213272095</v>
       </c>
       <c r="F8" t="n">
-        <v>2.481196880340576</v>
+        <v>2.325031280517578</v>
       </c>
       <c r="G8" t="n">
-        <v>2.303531408309937</v>
+        <v>2.575350284576416</v>
       </c>
       <c r="H8" t="n">
-        <v>2.234985589981079</v>
+        <v>2.635149478912354</v>
       </c>
       <c r="I8" t="n">
-        <v>2.412312984466553</v>
+        <v>2.43686580657959</v>
       </c>
       <c r="J8" t="n">
-        <v>2.392947196960449</v>
+        <v>2.549983739852905</v>
       </c>
       <c r="K8" t="n">
-        <v>2.401974201202393</v>
+        <v>2.416925430297852</v>
       </c>
       <c r="L8" t="n">
-        <v>2.403535628318787</v>
+        <v>2.454849433898926</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>2.363131761550903</v>
+        <v>2.31821084022522</v>
       </c>
       <c r="C9" t="n">
-        <v>2.219826698303223</v>
+        <v>2.406802654266357</v>
       </c>
       <c r="D9" t="n">
-        <v>2.604845523834229</v>
+        <v>2.284988403320312</v>
       </c>
       <c r="E9" t="n">
-        <v>2.352648735046387</v>
+        <v>2.500755786895752</v>
       </c>
       <c r="F9" t="n">
-        <v>2.410170793533325</v>
+        <v>2.560648679733276</v>
       </c>
       <c r="G9" t="n">
-        <v>2.339000463485718</v>
+        <v>2.221638202667236</v>
       </c>
       <c r="H9" t="n">
-        <v>2.295499086380005</v>
+        <v>2.470533847808838</v>
       </c>
       <c r="I9" t="n">
-        <v>2.305512189865112</v>
+        <v>2.383565902709961</v>
       </c>
       <c r="J9" t="n">
-        <v>2.24690580368042</v>
+        <v>2.326572418212891</v>
       </c>
       <c r="K9" t="n">
-        <v>2.419520378112793</v>
+        <v>2.532732963562012</v>
       </c>
       <c r="L9" t="n">
-        <v>2.355706143379211</v>
+        <v>2.400644969940186</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>2.376016855239868</v>
+        <v>2.340264558792114</v>
       </c>
       <c r="C10" t="n">
-        <v>2.401520967483521</v>
+        <v>2.419334888458252</v>
       </c>
       <c r="D10" t="n">
-        <v>2.428979635238647</v>
+        <v>2.948830604553223</v>
       </c>
       <c r="E10" t="n">
-        <v>2.300199270248413</v>
+        <v>2.498102188110352</v>
       </c>
       <c r="F10" t="n">
-        <v>2.280524253845215</v>
+        <v>2.414849996566772</v>
       </c>
       <c r="G10" t="n">
-        <v>2.403686046600342</v>
+        <v>2.364164352416992</v>
       </c>
       <c r="H10" t="n">
-        <v>2.549124717712402</v>
+        <v>2.558089733123779</v>
       </c>
       <c r="I10" t="n">
-        <v>2.433635473251343</v>
+        <v>2.502440690994263</v>
       </c>
       <c r="J10" t="n">
-        <v>2.176865339279175</v>
+        <v>2.386023044586182</v>
       </c>
       <c r="K10" t="n">
-        <v>2.218910694122314</v>
+        <v>2.523888826370239</v>
       </c>
       <c r="L10" t="n">
-        <v>2.356946325302124</v>
+        <v>2.495598888397217</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>1.889724493026733</v>
+        <v>2.045811653137207</v>
       </c>
       <c r="C11" t="n">
-        <v>1.96998119354248</v>
+        <v>2.111302614212036</v>
       </c>
       <c r="D11" t="n">
-        <v>1.885915279388428</v>
+        <v>2.020121335983276</v>
       </c>
       <c r="E11" t="n">
-        <v>1.909266233444214</v>
+        <v>2.050735950469971</v>
       </c>
       <c r="F11" t="n">
-        <v>2.042990207672119</v>
+        <v>2.03859806060791</v>
       </c>
       <c r="G11" t="n">
-        <v>2.035505056381226</v>
+        <v>1.944042921066284</v>
       </c>
       <c r="H11" t="n">
-        <v>1.986969232559204</v>
+        <v>1.975438117980957</v>
       </c>
       <c r="I11" t="n">
-        <v>1.844203472137451</v>
+        <v>2.067283391952515</v>
       </c>
       <c r="J11" t="n">
-        <v>1.900045156478882</v>
+        <v>2.00886607170105</v>
       </c>
       <c r="K11" t="n">
-        <v>2.174461603164673</v>
+        <v>2.062904119491577</v>
       </c>
       <c r="L11" t="n">
-        <v>1.963906192779541</v>
+        <v>2.032510423660278</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>2.338308811187744</v>
+        <v>2.408869504928589</v>
       </c>
       <c r="C12" t="n">
-        <v>2.246729373931885</v>
+        <v>2.578072071075439</v>
       </c>
       <c r="D12" t="n">
-        <v>2.299135684967041</v>
+        <v>2.249303817749023</v>
       </c>
       <c r="E12" t="n">
-        <v>2.269123554229736</v>
+        <v>2.50825047492981</v>
       </c>
       <c r="F12" t="n">
-        <v>2.351857662200928</v>
+        <v>2.247801542282104</v>
       </c>
       <c r="G12" t="n">
-        <v>2.215243339538574</v>
+        <v>2.466001749038696</v>
       </c>
       <c r="H12" t="n">
-        <v>2.191413879394531</v>
+        <v>2.352641582489014</v>
       </c>
       <c r="I12" t="n">
-        <v>2.516380548477173</v>
+        <v>2.270123720169067</v>
       </c>
       <c r="J12" t="n">
-        <v>2.160813331604004</v>
+        <v>2.563293695449829</v>
       </c>
       <c r="K12" t="n">
-        <v>2.562466144561768</v>
+        <v>2.405275583267212</v>
       </c>
       <c r="L12" t="n">
-        <v>2.315147233009339</v>
+        <v>2.404963374137878</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>2.27714729309082</v>
+        <v>2.465819120407104</v>
       </c>
       <c r="C13" t="n">
-        <v>2.314514636993408</v>
+        <v>2.324524164199829</v>
       </c>
       <c r="D13" t="n">
-        <v>2.333307027816772</v>
+        <v>2.47577977180481</v>
       </c>
       <c r="E13" t="n">
-        <v>2.423873901367188</v>
+        <v>2.455327272415161</v>
       </c>
       <c r="F13" t="n">
-        <v>2.495682954788208</v>
+        <v>2.557842254638672</v>
       </c>
       <c r="G13" t="n">
-        <v>2.271771907806396</v>
+        <v>2.373321533203125</v>
       </c>
       <c r="H13" t="n">
-        <v>2.343676567077637</v>
+        <v>2.891614675521851</v>
       </c>
       <c r="I13" t="n">
-        <v>2.366803407669067</v>
+        <v>2.593849658966064</v>
       </c>
       <c r="J13" t="n">
-        <v>2.339666604995728</v>
+        <v>2.316297769546509</v>
       </c>
       <c r="K13" t="n">
-        <v>2.248679161071777</v>
+        <v>2.570990562438965</v>
       </c>
       <c r="L13" t="n">
-        <v>2.3415123462677</v>
+        <v>2.502536678314209</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>2.370153903961182</v>
+        <v>2.397266864776611</v>
       </c>
       <c r="C14" t="n">
-        <v>2.340085744857788</v>
+        <v>2.478132724761963</v>
       </c>
       <c r="D14" t="n">
-        <v>2.45593786239624</v>
+        <v>2.705570459365845</v>
       </c>
       <c r="E14" t="n">
-        <v>2.33320426940918</v>
+        <v>2.348133087158203</v>
       </c>
       <c r="F14" t="n">
-        <v>2.299760103225708</v>
+        <v>2.381772041320801</v>
       </c>
       <c r="G14" t="n">
-        <v>2.39786958694458</v>
+        <v>2.638477325439453</v>
       </c>
       <c r="H14" t="n">
-        <v>2.293853998184204</v>
+        <v>2.471148490905762</v>
       </c>
       <c r="I14" t="n">
-        <v>2.288455486297607</v>
+        <v>2.459656238555908</v>
       </c>
       <c r="J14" t="n">
-        <v>2.427440643310547</v>
+        <v>2.26792311668396</v>
       </c>
       <c r="K14" t="n">
-        <v>2.173194169998169</v>
+        <v>2.47401762008667</v>
       </c>
       <c r="L14" t="n">
-        <v>2.33799557685852</v>
+        <v>2.462209796905518</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>2.208195924758911</v>
+        <v>2.257109403610229</v>
       </c>
       <c r="C15" t="n">
-        <v>2.183971166610718</v>
+        <v>2.289211750030518</v>
       </c>
       <c r="D15" t="n">
-        <v>2.287383794784546</v>
+        <v>2.295006990432739</v>
       </c>
       <c r="E15" t="n">
-        <v>2.288749217987061</v>
+        <v>2.367647886276245</v>
       </c>
       <c r="F15" t="n">
-        <v>2.274135828018188</v>
+        <v>2.211659669876099</v>
       </c>
       <c r="G15" t="n">
-        <v>2.445954084396362</v>
+        <v>2.275694131851196</v>
       </c>
       <c r="H15" t="n">
-        <v>2.141830921173096</v>
+        <v>2.210792779922485</v>
       </c>
       <c r="I15" t="n">
-        <v>2.15110969543457</v>
+        <v>2.250167846679688</v>
       </c>
       <c r="J15" t="n">
-        <v>2.208374261856079</v>
+        <v>2.268019437789917</v>
       </c>
       <c r="K15" t="n">
-        <v>2.195879697799683</v>
+        <v>2.19511079788208</v>
       </c>
       <c r="L15" t="n">
-        <v>2.238558459281921</v>
+        <v>2.26204206943512</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>2.346590518951416</v>
+        <v>2.343806028366089</v>
       </c>
       <c r="C16" t="n">
-        <v>2.240342855453491</v>
+        <v>2.670113801956177</v>
       </c>
       <c r="D16" t="n">
-        <v>2.280962705612183</v>
+        <v>2.420805215835571</v>
       </c>
       <c r="E16" t="n">
-        <v>2.258896827697754</v>
+        <v>2.385796070098877</v>
       </c>
       <c r="F16" t="n">
-        <v>2.405153751373291</v>
+        <v>2.423915863037109</v>
       </c>
       <c r="G16" t="n">
-        <v>2.351284980773926</v>
+        <v>2.423611402511597</v>
       </c>
       <c r="H16" t="n">
-        <v>2.47244119644165</v>
+        <v>2.488525629043579</v>
       </c>
       <c r="I16" t="n">
-        <v>2.506420612335205</v>
+        <v>2.416497468948364</v>
       </c>
       <c r="J16" t="n">
-        <v>2.496160507202148</v>
+        <v>2.655831575393677</v>
       </c>
       <c r="K16" t="n">
-        <v>2.282652139663696</v>
+        <v>2.418740749359131</v>
       </c>
       <c r="L16" t="n">
-        <v>2.364090609550476</v>
+        <v>2.464764380455017</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>2.541179418563843</v>
+        <v>2.159461498260498</v>
       </c>
       <c r="C17" t="n">
-        <v>2.753461837768555</v>
+        <v>2.334978342056274</v>
       </c>
       <c r="D17" t="n">
-        <v>2.154558897018433</v>
+        <v>2.48963737487793</v>
       </c>
       <c r="E17" t="n">
-        <v>2.311340570449829</v>
+        <v>2.577600955963135</v>
       </c>
       <c r="F17" t="n">
-        <v>2.106277465820312</v>
+        <v>2.870363712310791</v>
       </c>
       <c r="G17" t="n">
-        <v>2.085022926330566</v>
+        <v>2.292502880096436</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3253173828125</v>
+        <v>2.367166996002197</v>
       </c>
       <c r="I17" t="n">
-        <v>2.275068044662476</v>
+        <v>2.649836778640747</v>
       </c>
       <c r="J17" t="n">
-        <v>2.347215890884399</v>
+        <v>2.279807090759277</v>
       </c>
       <c r="K17" t="n">
-        <v>2.285014867782593</v>
+        <v>2.630986928939819</v>
       </c>
       <c r="L17" t="n">
-        <v>2.31844573020935</v>
+        <v>2.465234255790711</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>2.492417573928833</v>
+        <v>2.741695165634155</v>
       </c>
       <c r="C18" t="n">
-        <v>2.691219091415405</v>
+        <v>2.698764562606812</v>
       </c>
       <c r="D18" t="n">
-        <v>2.401197910308838</v>
+        <v>2.859166622161865</v>
       </c>
       <c r="E18" t="n">
-        <v>2.557161331176758</v>
+        <v>2.66983699798584</v>
       </c>
       <c r="F18" t="n">
-        <v>2.456440925598145</v>
+        <v>2.76374888420105</v>
       </c>
       <c r="G18" t="n">
-        <v>2.852356433868408</v>
+        <v>2.67120885848999</v>
       </c>
       <c r="H18" t="n">
-        <v>2.495139837265015</v>
+        <v>2.654865503311157</v>
       </c>
       <c r="I18" t="n">
-        <v>2.51653003692627</v>
+        <v>2.618453025817871</v>
       </c>
       <c r="J18" t="n">
-        <v>2.383969306945801</v>
+        <v>2.950462341308594</v>
       </c>
       <c r="K18" t="n">
-        <v>2.498739004135132</v>
+        <v>2.785674095153809</v>
       </c>
       <c r="L18" t="n">
-        <v>2.53451714515686</v>
+        <v>2.741387605667114</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>2.611307382583618</v>
+        <v>2.250212669372559</v>
       </c>
       <c r="C19" t="n">
-        <v>2.557816028594971</v>
+        <v>2.593358993530273</v>
       </c>
       <c r="D19" t="n">
-        <v>2.334461450576782</v>
+        <v>2.342833995819092</v>
       </c>
       <c r="E19" t="n">
-        <v>2.366632699966431</v>
+        <v>2.193773031234741</v>
       </c>
       <c r="F19" t="n">
-        <v>2.373235940933228</v>
+        <v>2.304755449295044</v>
       </c>
       <c r="G19" t="n">
-        <v>2.560867309570312</v>
+        <v>2.494577646255493</v>
       </c>
       <c r="H19" t="n">
-        <v>2.463188886642456</v>
+        <v>2.562633037567139</v>
       </c>
       <c r="I19" t="n">
-        <v>2.087486028671265</v>
+        <v>2.356989145278931</v>
       </c>
       <c r="J19" t="n">
-        <v>2.475757598876953</v>
+        <v>2.262911558151245</v>
       </c>
       <c r="K19" t="n">
-        <v>2.099258422851562</v>
+        <v>2.460984230041504</v>
       </c>
       <c r="L19" t="n">
-        <v>2.393001174926758</v>
+        <v>2.382302975654602</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>2.243327379226685</v>
+        <v>2.584047794342041</v>
       </c>
       <c r="C20" t="n">
-        <v>2.563045024871826</v>
+        <v>2.568546533584595</v>
       </c>
       <c r="D20" t="n">
-        <v>2.542411327362061</v>
+        <v>2.375766277313232</v>
       </c>
       <c r="E20" t="n">
-        <v>2.574748039245605</v>
+        <v>2.236759424209595</v>
       </c>
       <c r="F20" t="n">
-        <v>2.262568712234497</v>
+        <v>2.536314249038696</v>
       </c>
       <c r="G20" t="n">
-        <v>2.309859991073608</v>
+        <v>2.48577094078064</v>
       </c>
       <c r="H20" t="n">
-        <v>2.265493154525757</v>
+        <v>2.498158931732178</v>
       </c>
       <c r="I20" t="n">
-        <v>2.239013910293579</v>
+        <v>2.426128625869751</v>
       </c>
       <c r="J20" t="n">
-        <v>2.30009913444519</v>
+        <v>2.684597253799438</v>
       </c>
       <c r="K20" t="n">
-        <v>2.268992900848389</v>
+        <v>2.541943073272705</v>
       </c>
       <c r="L20" t="n">
-        <v>2.35695595741272</v>
+        <v>2.493803310394287</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>2.36072826385498</v>
+        <v>2.463896751403809</v>
       </c>
       <c r="C21" t="n">
-        <v>2.474902868270874</v>
+        <v>2.376632690429688</v>
       </c>
       <c r="D21" t="n">
-        <v>2.521971464157104</v>
+        <v>2.333667278289795</v>
       </c>
       <c r="E21" t="n">
-        <v>2.232264995574951</v>
+        <v>2.573249816894531</v>
       </c>
       <c r="F21" t="n">
-        <v>2.409966707229614</v>
+        <v>2.317851781845093</v>
       </c>
       <c r="G21" t="n">
-        <v>2.616458177566528</v>
+        <v>2.661033868789673</v>
       </c>
       <c r="H21" t="n">
-        <v>2.430205821990967</v>
+        <v>2.466113567352295</v>
       </c>
       <c r="I21" t="n">
-        <v>2.217196702957153</v>
+        <v>2.511523485183716</v>
       </c>
       <c r="J21" t="n">
-        <v>2.261895656585693</v>
+        <v>2.425406932830811</v>
       </c>
       <c r="K21" t="n">
-        <v>2.401279211044312</v>
+        <v>2.557217597961426</v>
       </c>
       <c r="L21" t="n">
-        <v>2.392686986923218</v>
+        <v>2.468659377098084</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>2.24213171005249</v>
+        <v>2.343028783798218</v>
       </c>
       <c r="C22" t="n">
-        <v>2.035986423492432</v>
+        <v>2.293648242950439</v>
       </c>
       <c r="D22" t="n">
-        <v>2.247570276260376</v>
+        <v>2.268950223922729</v>
       </c>
       <c r="E22" t="n">
-        <v>2.132565021514893</v>
+        <v>2.227612257003784</v>
       </c>
       <c r="F22" t="n">
-        <v>2.192919492721558</v>
+        <v>2.286376953125</v>
       </c>
       <c r="G22" t="n">
-        <v>2.063910007476807</v>
+        <v>2.510490417480469</v>
       </c>
       <c r="H22" t="n">
-        <v>2.133724451065063</v>
+        <v>2.310420036315918</v>
       </c>
       <c r="I22" t="n">
-        <v>2.230497598648071</v>
+        <v>2.098490953445435</v>
       </c>
       <c r="J22" t="n">
-        <v>2.211252450942993</v>
+        <v>2.308674573898315</v>
       </c>
       <c r="K22" t="n">
-        <v>2.203205347061157</v>
+        <v>2.261834859848022</v>
       </c>
       <c r="L22" t="n">
-        <v>2.169376277923584</v>
+        <v>2.290952730178833</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>2.160553455352783</v>
+        <v>2.114242553710938</v>
       </c>
       <c r="C23" t="n">
-        <v>2.109716176986694</v>
+        <v>2.155123472213745</v>
       </c>
       <c r="D23" t="n">
-        <v>2.116111040115356</v>
+        <v>2.229286193847656</v>
       </c>
       <c r="E23" t="n">
-        <v>2.225071668624878</v>
+        <v>2.277075529098511</v>
       </c>
       <c r="F23" t="n">
-        <v>2.148640155792236</v>
+        <v>2.259047031402588</v>
       </c>
       <c r="G23" t="n">
-        <v>2.00386643409729</v>
+        <v>2.212797403335571</v>
       </c>
       <c r="H23" t="n">
-        <v>1.98231053352356</v>
+        <v>2.170983791351318</v>
       </c>
       <c r="I23" t="n">
-        <v>2.056936979293823</v>
+        <v>2.17541241645813</v>
       </c>
       <c r="J23" t="n">
-        <v>2.12772274017334</v>
+        <v>2.173081398010254</v>
       </c>
       <c r="K23" t="n">
-        <v>2.021164894104004</v>
+        <v>2.120071887969971</v>
       </c>
       <c r="L23" t="n">
-        <v>2.095209407806396</v>
+        <v>2.188712167739868</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>2.075005054473877</v>
+        <v>2.236929655075073</v>
       </c>
       <c r="C24" t="n">
-        <v>2.117825031280518</v>
+        <v>2.176482677459717</v>
       </c>
       <c r="D24" t="n">
-        <v>2.04400372505188</v>
+        <v>2.125473737716675</v>
       </c>
       <c r="E24" t="n">
-        <v>2.065030813217163</v>
+        <v>2.235109567642212</v>
       </c>
       <c r="F24" t="n">
-        <v>1.942157506942749</v>
+        <v>2.226937294006348</v>
       </c>
       <c r="G24" t="n">
-        <v>2.030595541000366</v>
+        <v>2.161561012268066</v>
       </c>
       <c r="H24" t="n">
-        <v>2.016123056411743</v>
+        <v>2.18537974357605</v>
       </c>
       <c r="I24" t="n">
-        <v>2.04699969291687</v>
+        <v>2.329382419586182</v>
       </c>
       <c r="J24" t="n">
-        <v>2.164159297943115</v>
+        <v>2.091409206390381</v>
       </c>
       <c r="K24" t="n">
-        <v>2.147177934646606</v>
+        <v>2.253072738647461</v>
       </c>
       <c r="L24" t="n">
-        <v>2.064907765388489</v>
+        <v>2.202173805236816</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>2.051251173019409</v>
+        <v>2.426297187805176</v>
       </c>
       <c r="C25" t="n">
-        <v>2.268868446350098</v>
+        <v>2.328776121139526</v>
       </c>
       <c r="D25" t="n">
-        <v>2.25214672088623</v>
+        <v>2.319185972213745</v>
       </c>
       <c r="E25" t="n">
-        <v>2.101739883422852</v>
+        <v>2.116929054260254</v>
       </c>
       <c r="F25" t="n">
-        <v>2.41633677482605</v>
+        <v>2.183006525039673</v>
       </c>
       <c r="G25" t="n">
-        <v>2.369232177734375</v>
+        <v>2.423719167709351</v>
       </c>
       <c r="H25" t="n">
-        <v>2.369036197662354</v>
+        <v>2.415958881378174</v>
       </c>
       <c r="I25" t="n">
-        <v>2.290084600448608</v>
+        <v>2.237166166305542</v>
       </c>
       <c r="J25" t="n">
-        <v>2.430293560028076</v>
+        <v>2.467694044113159</v>
       </c>
       <c r="K25" t="n">
-        <v>2.218044757843018</v>
+        <v>2.580307483673096</v>
       </c>
       <c r="L25" t="n">
-        <v>2.276703429222107</v>
+        <v>2.34990406036377</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>2.311670303344727</v>
+        <v>2.749488592147827</v>
       </c>
       <c r="C26" t="n">
-        <v>2.373588562011719</v>
+        <v>2.399746656417847</v>
       </c>
       <c r="D26" t="n">
-        <v>2.38218879699707</v>
+        <v>2.707794189453125</v>
       </c>
       <c r="E26" t="n">
-        <v>2.678719520568848</v>
+        <v>2.507285356521606</v>
       </c>
       <c r="F26" t="n">
-        <v>2.545140027999878</v>
+        <v>2.480725765228271</v>
       </c>
       <c r="G26" t="n">
-        <v>2.57115626335144</v>
+        <v>2.751431941986084</v>
       </c>
       <c r="H26" t="n">
-        <v>2.505676746368408</v>
+        <v>2.689064741134644</v>
       </c>
       <c r="I26" t="n">
-        <v>2.555432319641113</v>
+        <v>2.496855497360229</v>
       </c>
       <c r="J26" t="n">
-        <v>2.339131832122803</v>
+        <v>2.738102197647095</v>
       </c>
       <c r="K26" t="n">
-        <v>2.377584934234619</v>
+        <v>2.443025827407837</v>
       </c>
       <c r="L26" t="n">
-        <v>2.464028930664063</v>
+        <v>2.596352076530457</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>2.271225452423096</v>
+        <v>2.238811492919922</v>
       </c>
       <c r="C27" t="n">
-        <v>2.081384420394897</v>
+        <v>2.116111040115356</v>
       </c>
       <c r="D27" t="n">
-        <v>2.032072305679321</v>
+        <v>2.598213672637939</v>
       </c>
       <c r="E27" t="n">
-        <v>2.083369016647339</v>
+        <v>2.339792013168335</v>
       </c>
       <c r="F27" t="n">
-        <v>2.238334178924561</v>
+        <v>2.169579744338989</v>
       </c>
       <c r="G27" t="n">
-        <v>2.269001722335815</v>
+        <v>2.246803760528564</v>
       </c>
       <c r="H27" t="n">
-        <v>2.320241451263428</v>
+        <v>2.271059513092041</v>
       </c>
       <c r="I27" t="n">
-        <v>2.238147020339966</v>
+        <v>2.481401443481445</v>
       </c>
       <c r="J27" t="n">
-        <v>2.497352600097656</v>
+        <v>2.303827047348022</v>
       </c>
       <c r="K27" t="n">
-        <v>2.139922857284546</v>
+        <v>2.204832792282104</v>
       </c>
       <c r="L27" t="n">
-        <v>2.217105102539063</v>
+        <v>2.297043251991272</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>2.220102787017822</v>
+        <v>2.362714529037476</v>
       </c>
       <c r="C28" t="n">
-        <v>2.185099363327026</v>
+        <v>2.334725141525269</v>
       </c>
       <c r="D28" t="n">
-        <v>2.157973527908325</v>
+        <v>2.257221221923828</v>
       </c>
       <c r="E28" t="n">
-        <v>2.089006423950195</v>
+        <v>2.25852370262146</v>
       </c>
       <c r="F28" t="n">
-        <v>2.226289033889771</v>
+        <v>2.265795230865479</v>
       </c>
       <c r="G28" t="n">
-        <v>2.114748239517212</v>
+        <v>2.313092470169067</v>
       </c>
       <c r="H28" t="n">
-        <v>2.092259168624878</v>
+        <v>2.319825649261475</v>
       </c>
       <c r="I28" t="n">
-        <v>2.270565748214722</v>
+        <v>2.30683159828186</v>
       </c>
       <c r="J28" t="n">
-        <v>2.214496850967407</v>
+        <v>2.314684629440308</v>
       </c>
       <c r="K28" t="n">
-        <v>2.228266954421997</v>
+        <v>2.483938694000244</v>
       </c>
       <c r="L28" t="n">
-        <v>2.179880809783936</v>
+        <v>2.321735286712646</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>2.179438829421997</v>
+        <v>2.211318492889404</v>
       </c>
       <c r="C29" t="n">
-        <v>2.399741888046265</v>
+        <v>2.416282653808594</v>
       </c>
       <c r="D29" t="n">
-        <v>2.290882110595703</v>
+        <v>2.279379606246948</v>
       </c>
       <c r="E29" t="n">
-        <v>2.550350189208984</v>
+        <v>2.265898466110229</v>
       </c>
       <c r="F29" t="n">
-        <v>2.467635869979858</v>
+        <v>2.203520536422729</v>
       </c>
       <c r="G29" t="n">
-        <v>2.285593748092651</v>
+        <v>2.245791435241699</v>
       </c>
       <c r="H29" t="n">
-        <v>2.205209255218506</v>
+        <v>2.256207227706909</v>
       </c>
       <c r="I29" t="n">
-        <v>2.177493810653687</v>
+        <v>2.320796966552734</v>
       </c>
       <c r="J29" t="n">
-        <v>2.141035318374634</v>
+        <v>2.225744724273682</v>
       </c>
       <c r="K29" t="n">
-        <v>2.206588268280029</v>
+        <v>2.152972459793091</v>
       </c>
       <c r="L29" t="n">
-        <v>2.290396928787231</v>
+        <v>2.257791256904602</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>2.385423421859741</v>
+        <v>2.228159189224243</v>
       </c>
       <c r="C30" t="n">
-        <v>2.525074243545532</v>
+        <v>2.349575042724609</v>
       </c>
       <c r="D30" t="n">
-        <v>2.249408721923828</v>
+        <v>2.602716207504272</v>
       </c>
       <c r="E30" t="n">
-        <v>2.506054162979126</v>
+        <v>2.601083040237427</v>
       </c>
       <c r="F30" t="n">
-        <v>2.640724182128906</v>
+        <v>2.216597318649292</v>
       </c>
       <c r="G30" t="n">
-        <v>2.621291160583496</v>
+        <v>2.285028457641602</v>
       </c>
       <c r="H30" t="n">
-        <v>2.264275074005127</v>
+        <v>2.477516651153564</v>
       </c>
       <c r="I30" t="n">
-        <v>2.172221660614014</v>
+        <v>2.532262086868286</v>
       </c>
       <c r="J30" t="n">
-        <v>2.332626581192017</v>
+        <v>2.570489168167114</v>
       </c>
       <c r="K30" t="n">
-        <v>2.208988428115845</v>
+        <v>2.260596990585327</v>
       </c>
       <c r="L30" t="n">
-        <v>2.390608763694763</v>
+        <v>2.412402415275574</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>1.994751930236816</v>
+        <v>2.074937582015991</v>
       </c>
       <c r="C31" t="n">
-        <v>1.980176687240601</v>
+        <v>2.040514469146729</v>
       </c>
       <c r="D31" t="n">
-        <v>2.033284664154053</v>
+        <v>1.938896894454956</v>
       </c>
       <c r="E31" t="n">
-        <v>2.018971681594849</v>
+        <v>1.984498739242554</v>
       </c>
       <c r="F31" t="n">
-        <v>1.889735460281372</v>
+        <v>1.927890300750732</v>
       </c>
       <c r="G31" t="n">
-        <v>1.88872504234314</v>
+        <v>2.106884717941284</v>
       </c>
       <c r="H31" t="n">
-        <v>2.049720525741577</v>
+        <v>2.06678295135498</v>
       </c>
       <c r="I31" t="n">
-        <v>1.875363349914551</v>
+        <v>2.020469188690186</v>
       </c>
       <c r="J31" t="n">
-        <v>1.956488370895386</v>
+        <v>1.988327026367188</v>
       </c>
       <c r="K31" t="n">
-        <v>1.930954456329346</v>
+        <v>1.968703269958496</v>
       </c>
       <c r="L31" t="n">
-        <v>1.961817216873169</v>
+        <v>2.01179051399231</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>1.971256017684937</v>
+        <v>2.218030691146851</v>
       </c>
       <c r="C32" t="n">
-        <v>2.100401401519775</v>
+        <v>2.279978513717651</v>
       </c>
       <c r="D32" t="n">
-        <v>2.044101476669312</v>
+        <v>2.171908378601074</v>
       </c>
       <c r="E32" t="n">
-        <v>1.93900728225708</v>
+        <v>2.14684534072876</v>
       </c>
       <c r="F32" t="n">
-        <v>2.078348875045776</v>
+        <v>2.069884538650513</v>
       </c>
       <c r="G32" t="n">
-        <v>2.339494943618774</v>
+        <v>2.197428703308105</v>
       </c>
       <c r="H32" t="n">
-        <v>2.009339809417725</v>
+        <v>2.183190107345581</v>
       </c>
       <c r="I32" t="n">
-        <v>2.050056219100952</v>
+        <v>2.261255979537964</v>
       </c>
       <c r="J32" t="n">
-        <v>2.181708335876465</v>
+        <v>2.365084648132324</v>
       </c>
       <c r="K32" t="n">
-        <v>2.313326835632324</v>
+        <v>2.201997756958008</v>
       </c>
       <c r="L32" t="n">
-        <v>2.102704119682312</v>
+        <v>2.209560465812683</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>2.278043985366821</v>
+        <v>2.497686624526978</v>
       </c>
       <c r="C33" t="n">
-        <v>2.45987606048584</v>
+        <v>2.464184999465942</v>
       </c>
       <c r="D33" t="n">
-        <v>2.214119672775269</v>
+        <v>2.264735460281372</v>
       </c>
       <c r="E33" t="n">
-        <v>2.280383110046387</v>
+        <v>2.379871129989624</v>
       </c>
       <c r="F33" t="n">
-        <v>2.228001594543457</v>
+        <v>2.392287492752075</v>
       </c>
       <c r="G33" t="n">
-        <v>2.281618118286133</v>
+        <v>2.12110710144043</v>
       </c>
       <c r="H33" t="n">
-        <v>2.121392726898193</v>
+        <v>2.339218378067017</v>
       </c>
       <c r="I33" t="n">
-        <v>2.209851026535034</v>
+        <v>2.406780004501343</v>
       </c>
       <c r="J33" t="n">
-        <v>2.316862344741821</v>
+        <v>2.322880744934082</v>
       </c>
       <c r="K33" t="n">
-        <v>2.27036714553833</v>
+        <v>2.286093711853027</v>
       </c>
       <c r="L33" t="n">
-        <v>2.266051578521728</v>
+        <v>2.347484564781189</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>2.017218828201294</v>
+        <v>2.019038200378418</v>
       </c>
       <c r="C34" t="n">
-        <v>2.04112696647644</v>
+        <v>2.03258228302002</v>
       </c>
       <c r="D34" t="n">
-        <v>2.014444828033447</v>
+        <v>2.186257362365723</v>
       </c>
       <c r="E34" t="n">
-        <v>2.154292106628418</v>
+        <v>2.232968091964722</v>
       </c>
       <c r="F34" t="n">
-        <v>1.988901853561401</v>
+        <v>2.073772668838501</v>
       </c>
       <c r="G34" t="n">
-        <v>2.052521944046021</v>
+        <v>2.073939085006714</v>
       </c>
       <c r="H34" t="n">
-        <v>1.986527442932129</v>
+        <v>2.062020778656006</v>
       </c>
       <c r="I34" t="n">
-        <v>1.923195838928223</v>
+        <v>2.059449672698975</v>
       </c>
       <c r="J34" t="n">
-        <v>1.995953559875488</v>
+        <v>2.123263120651245</v>
       </c>
       <c r="K34" t="n">
-        <v>2.109824895858765</v>
+        <v>1.98289966583252</v>
       </c>
       <c r="L34" t="n">
-        <v>2.028400826454162</v>
+        <v>2.084619092941284</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>2.422574520111084</v>
+        <v>2.480749368667603</v>
       </c>
       <c r="C35" t="n">
-        <v>2.615258932113647</v>
+        <v>2.467183828353882</v>
       </c>
       <c r="D35" t="n">
-        <v>2.586704730987549</v>
+        <v>2.521485805511475</v>
       </c>
       <c r="E35" t="n">
-        <v>2.566464424133301</v>
+        <v>2.663989305496216</v>
       </c>
       <c r="F35" t="n">
-        <v>2.539531469345093</v>
+        <v>2.492948055267334</v>
       </c>
       <c r="G35" t="n">
-        <v>2.658814430236816</v>
+        <v>2.506383895874023</v>
       </c>
       <c r="H35" t="n">
-        <v>2.541337966918945</v>
+        <v>2.728344917297363</v>
       </c>
       <c r="I35" t="n">
-        <v>2.526705741882324</v>
+        <v>2.461073875427246</v>
       </c>
       <c r="J35" t="n">
-        <v>2.476305484771729</v>
+        <v>2.495628356933594</v>
       </c>
       <c r="K35" t="n">
-        <v>2.500962018966675</v>
+        <v>2.431413888931274</v>
       </c>
       <c r="L35" t="n">
-        <v>2.543465971946716</v>
+        <v>2.524920129776001</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>1.977578639984131</v>
+        <v>2.14766526222229</v>
       </c>
       <c r="C36" t="n">
-        <v>2.053935050964355</v>
+        <v>2.122676849365234</v>
       </c>
       <c r="D36" t="n">
-        <v>2.129997968673706</v>
+        <v>2.004938364028931</v>
       </c>
       <c r="E36" t="n">
-        <v>2.045824289321899</v>
+        <v>2.166963815689087</v>
       </c>
       <c r="F36" t="n">
-        <v>1.999403238296509</v>
+        <v>2.110007524490356</v>
       </c>
       <c r="G36" t="n">
-        <v>1.942238807678223</v>
+        <v>2.144822359085083</v>
       </c>
       <c r="H36" t="n">
-        <v>2.088749170303345</v>
+        <v>2.113300323486328</v>
       </c>
       <c r="I36" t="n">
-        <v>2.072255611419678</v>
+        <v>2.239610910415649</v>
       </c>
       <c r="J36" t="n">
-        <v>2.087782144546509</v>
+        <v>2.147632122039795</v>
       </c>
       <c r="K36" t="n">
-        <v>1.980377912521362</v>
+        <v>2.150770425796509</v>
       </c>
       <c r="L36" t="n">
-        <v>2.037814283370972</v>
+        <v>2.134838795661926</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>2.458554744720459</v>
+        <v>2.398955345153809</v>
       </c>
       <c r="C37" t="n">
-        <v>2.288523197174072</v>
+        <v>2.484236717224121</v>
       </c>
       <c r="D37" t="n">
-        <v>2.420032262802124</v>
+        <v>2.348763465881348</v>
       </c>
       <c r="E37" t="n">
-        <v>2.672554492950439</v>
+        <v>2.520177125930786</v>
       </c>
       <c r="F37" t="n">
-        <v>2.427110195159912</v>
+        <v>2.422332525253296</v>
       </c>
       <c r="G37" t="n">
-        <v>2.340619802474976</v>
+        <v>2.559529066085815</v>
       </c>
       <c r="H37" t="n">
-        <v>2.442000865936279</v>
+        <v>2.393002033233643</v>
       </c>
       <c r="I37" t="n">
-        <v>2.314163684844971</v>
+        <v>2.344029426574707</v>
       </c>
       <c r="J37" t="n">
-        <v>2.411597013473511</v>
+        <v>2.610568761825562</v>
       </c>
       <c r="K37" t="n">
-        <v>2.528786182403564</v>
+        <v>2.415564775466919</v>
       </c>
       <c r="L37" t="n">
-        <v>2.430394244194031</v>
+        <v>2.449715924263001</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>2.775727272033691</v>
+        <v>2.669522523880005</v>
       </c>
       <c r="C38" t="n">
-        <v>2.722217321395874</v>
+        <v>2.822709321975708</v>
       </c>
       <c r="D38" t="n">
-        <v>2.736039876937866</v>
+        <v>2.896262645721436</v>
       </c>
       <c r="E38" t="n">
-        <v>2.563236713409424</v>
+        <v>2.883430004119873</v>
       </c>
       <c r="F38" t="n">
-        <v>2.659083604812622</v>
+        <v>2.786041021347046</v>
       </c>
       <c r="G38" t="n">
-        <v>2.632193326950073</v>
+        <v>2.735464334487915</v>
       </c>
       <c r="H38" t="n">
-        <v>2.587119102478027</v>
+        <v>2.631167888641357</v>
       </c>
       <c r="I38" t="n">
-        <v>2.468398571014404</v>
+        <v>2.633835077285767</v>
       </c>
       <c r="J38" t="n">
-        <v>2.781903505325317</v>
+        <v>2.649544477462769</v>
       </c>
       <c r="K38" t="n">
-        <v>2.682822704315186</v>
+        <v>2.666513919830322</v>
       </c>
       <c r="L38" t="n">
-        <v>2.660874199867249</v>
+        <v>2.73744912147522</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>2.360387325286865</v>
+        <v>2.404727935791016</v>
       </c>
       <c r="C39" t="n">
-        <v>2.394530057907104</v>
+        <v>2.391363620758057</v>
       </c>
       <c r="D39" t="n">
-        <v>2.285918951034546</v>
+        <v>2.330491304397583</v>
       </c>
       <c r="E39" t="n">
-        <v>2.411670684814453</v>
+        <v>2.358062744140625</v>
       </c>
       <c r="F39" t="n">
-        <v>2.525589227676392</v>
+        <v>2.490055561065674</v>
       </c>
       <c r="G39" t="n">
-        <v>3.076935768127441</v>
+        <v>2.362680196762085</v>
       </c>
       <c r="H39" t="n">
-        <v>2.604919195175171</v>
+        <v>2.476339340209961</v>
       </c>
       <c r="I39" t="n">
-        <v>2.682490110397339</v>
+        <v>2.537653923034668</v>
       </c>
       <c r="J39" t="n">
-        <v>2.521494626998901</v>
+        <v>2.418158769607544</v>
       </c>
       <c r="K39" t="n">
-        <v>2.444211483001709</v>
+        <v>2.495505332946777</v>
       </c>
       <c r="L39" t="n">
-        <v>2.530814743041992</v>
+        <v>2.426503872871399</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>2.365073919296265</v>
+        <v>2.230965852737427</v>
       </c>
       <c r="C40" t="n">
-        <v>2.152089357376099</v>
+        <v>2.102883815765381</v>
       </c>
       <c r="D40" t="n">
-        <v>2.061578750610352</v>
+        <v>2.267479181289673</v>
       </c>
       <c r="E40" t="n">
-        <v>2.259391784667969</v>
+        <v>2.360553979873657</v>
       </c>
       <c r="F40" t="n">
-        <v>2.200763702392578</v>
+        <v>2.236016511917114</v>
       </c>
       <c r="G40" t="n">
-        <v>2.531013250350952</v>
+        <v>2.325058221817017</v>
       </c>
       <c r="H40" t="n">
-        <v>2.235809564590454</v>
+        <v>2.288489818572998</v>
       </c>
       <c r="I40" t="n">
-        <v>2.199243307113647</v>
+        <v>2.205147981643677</v>
       </c>
       <c r="J40" t="n">
-        <v>2.271643161773682</v>
+        <v>2.37471079826355</v>
       </c>
       <c r="K40" t="n">
-        <v>2.188698053359985</v>
+        <v>2.20109748840332</v>
       </c>
       <c r="L40" t="n">
-        <v>2.246530485153198</v>
+        <v>2.259240365028381</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>2.514249563217163</v>
+        <v>2.493536710739136</v>
       </c>
       <c r="C41" t="n">
-        <v>2.551495790481567</v>
+        <v>2.544941425323486</v>
       </c>
       <c r="D41" t="n">
-        <v>2.710912466049194</v>
+        <v>2.428535938262939</v>
       </c>
       <c r="E41" t="n">
-        <v>2.512959480285645</v>
+        <v>2.472071170806885</v>
       </c>
       <c r="F41" t="n">
-        <v>2.525816917419434</v>
+        <v>2.506774187088013</v>
       </c>
       <c r="G41" t="n">
-        <v>2.278814077377319</v>
+        <v>2.50137996673584</v>
       </c>
       <c r="H41" t="n">
-        <v>2.496810913085938</v>
+        <v>2.501037120819092</v>
       </c>
       <c r="I41" t="n">
-        <v>2.632582426071167</v>
+        <v>2.547173500061035</v>
       </c>
       <c r="J41" t="n">
-        <v>2.528022527694702</v>
+        <v>2.438174486160278</v>
       </c>
       <c r="K41" t="n">
-        <v>2.437191724777222</v>
+        <v>2.573015213012695</v>
       </c>
       <c r="L41" t="n">
-        <v>2.518885588645935</v>
+        <v>2.50066397190094</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>2.077086687088013</v>
+        <v>2.146679162979126</v>
       </c>
       <c r="C42" t="n">
-        <v>2.011380910873413</v>
+        <v>2.221295118331909</v>
       </c>
       <c r="D42" t="n">
-        <v>2.090343236923218</v>
+        <v>2.166747808456421</v>
       </c>
       <c r="E42" t="n">
-        <v>2.211240768432617</v>
+        <v>2.176973581314087</v>
       </c>
       <c r="F42" t="n">
-        <v>2.071002721786499</v>
+        <v>2.26510763168335</v>
       </c>
       <c r="G42" t="n">
-        <v>2.077228307723999</v>
+        <v>2.151386737823486</v>
       </c>
       <c r="H42" t="n">
-        <v>2.102809190750122</v>
+        <v>2.098809480667114</v>
       </c>
       <c r="I42" t="n">
-        <v>2.149469137191772</v>
+        <v>2.136743068695068</v>
       </c>
       <c r="J42" t="n">
-        <v>2.160861730575562</v>
+        <v>2.108233690261841</v>
       </c>
       <c r="K42" t="n">
-        <v>1.974293231964111</v>
+        <v>2.147217988967896</v>
       </c>
       <c r="L42" t="n">
-        <v>2.092571592330933</v>
+        <v>2.16191942691803</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>2.389641761779785</v>
+        <v>2.423105478286743</v>
       </c>
       <c r="C43" t="n">
-        <v>2.746421337127686</v>
+        <v>2.640828132629395</v>
       </c>
       <c r="D43" t="n">
-        <v>2.473137855529785</v>
+        <v>2.406311750411987</v>
       </c>
       <c r="E43" t="n">
-        <v>2.18017053604126</v>
+        <v>2.487714290618896</v>
       </c>
       <c r="F43" t="n">
-        <v>2.500415802001953</v>
+        <v>2.368430852890015</v>
       </c>
       <c r="G43" t="n">
-        <v>2.485571622848511</v>
+        <v>2.335326910018921</v>
       </c>
       <c r="H43" t="n">
-        <v>2.396565675735474</v>
+        <v>2.385788202285767</v>
       </c>
       <c r="I43" t="n">
-        <v>2.269823551177979</v>
+        <v>2.529021739959717</v>
       </c>
       <c r="J43" t="n">
-        <v>2.24295711517334</v>
+        <v>2.503864526748657</v>
       </c>
       <c r="K43" t="n">
-        <v>2.160889387130737</v>
+        <v>2.304370403289795</v>
       </c>
       <c r="L43" t="n">
-        <v>2.384559464454651</v>
+        <v>2.438476228713989</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>2.304185390472412</v>
+        <v>2.216936826705933</v>
       </c>
       <c r="C44" t="n">
-        <v>2.199469804763794</v>
+        <v>2.176779985427856</v>
       </c>
       <c r="D44" t="n">
-        <v>2.134446382522583</v>
+        <v>2.217886686325073</v>
       </c>
       <c r="E44" t="n">
-        <v>2.261146783828735</v>
+        <v>2.210829734802246</v>
       </c>
       <c r="F44" t="n">
-        <v>2.173513889312744</v>
+        <v>2.102535724639893</v>
       </c>
       <c r="G44" t="n">
-        <v>2.111193180084229</v>
+        <v>2.309256792068481</v>
       </c>
       <c r="H44" t="n">
-        <v>2.267928600311279</v>
+        <v>2.20640754699707</v>
       </c>
       <c r="I44" t="n">
-        <v>2.189802169799805</v>
+        <v>2.280290365219116</v>
       </c>
       <c r="J44" t="n">
-        <v>2.19031286239624</v>
+        <v>2.314347982406616</v>
       </c>
       <c r="K44" t="n">
-        <v>2.15055513381958</v>
+        <v>2.305145025253296</v>
       </c>
       <c r="L44" t="n">
-        <v>2.19825541973114</v>
+        <v>2.234041666984558</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>2.068115949630737</v>
+        <v>2.245334625244141</v>
       </c>
       <c r="C45" t="n">
-        <v>2.098393440246582</v>
+        <v>2.307247161865234</v>
       </c>
       <c r="D45" t="n">
-        <v>1.964535236358643</v>
+        <v>2.097447395324707</v>
       </c>
       <c r="E45" t="n">
-        <v>2.038015127182007</v>
+        <v>2.027090787887573</v>
       </c>
       <c r="F45" t="n">
-        <v>1.983660697937012</v>
+        <v>2.002734661102295</v>
       </c>
       <c r="G45" t="n">
-        <v>2.207638740539551</v>
+        <v>2.08736777305603</v>
       </c>
       <c r="H45" t="n">
-        <v>2.195206642150879</v>
+        <v>2.149427652359009</v>
       </c>
       <c r="I45" t="n">
-        <v>2.153884172439575</v>
+        <v>2.311187267303467</v>
       </c>
       <c r="J45" t="n">
-        <v>2.292356014251709</v>
+        <v>2.024633646011353</v>
       </c>
       <c r="K45" t="n">
-        <v>2.126687049865723</v>
+        <v>2.189533472061157</v>
       </c>
       <c r="L45" t="n">
-        <v>2.112849307060242</v>
+        <v>2.144200444221497</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>1.909605026245117</v>
+        <v>2.170989990234375</v>
       </c>
       <c r="C46" t="n">
-        <v>1.883816957473755</v>
+        <v>2.031543731689453</v>
       </c>
       <c r="D46" t="n">
-        <v>2.082253456115723</v>
+        <v>1.909807920455933</v>
       </c>
       <c r="E46" t="n">
-        <v>2.110816240310669</v>
+        <v>1.89731764793396</v>
       </c>
       <c r="F46" t="n">
-        <v>1.936017990112305</v>
+        <v>2.187866687774658</v>
       </c>
       <c r="G46" t="n">
-        <v>2.029893159866333</v>
+        <v>2.083519220352173</v>
       </c>
       <c r="H46" t="n">
-        <v>1.85785436630249</v>
+        <v>2.157788991928101</v>
       </c>
       <c r="I46" t="n">
-        <v>2.214422225952148</v>
+        <v>1.934845924377441</v>
       </c>
       <c r="J46" t="n">
-        <v>2.048776865005493</v>
+        <v>2.267605066299438</v>
       </c>
       <c r="K46" t="n">
-        <v>1.9415442943573</v>
+        <v>2.038901090621948</v>
       </c>
       <c r="L46" t="n">
-        <v>2.001500058174133</v>
+        <v>2.068018627166748</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>2.879064321517944</v>
+        <v>2.878587484359741</v>
       </c>
       <c r="C47" t="n">
-        <v>2.726935148239136</v>
+        <v>3.061030864715576</v>
       </c>
       <c r="D47" t="n">
-        <v>2.483027458190918</v>
+        <v>2.698293685913086</v>
       </c>
       <c r="E47" t="n">
-        <v>2.980980157852173</v>
+        <v>2.638418674468994</v>
       </c>
       <c r="F47" t="n">
-        <v>2.804631471633911</v>
+        <v>2.840264797210693</v>
       </c>
       <c r="G47" t="n">
-        <v>3.252337217330933</v>
+        <v>3.051038980484009</v>
       </c>
       <c r="H47" t="n">
-        <v>2.621703624725342</v>
+        <v>3.21376371383667</v>
       </c>
       <c r="I47" t="n">
-        <v>2.656440496444702</v>
+        <v>2.723749876022339</v>
       </c>
       <c r="J47" t="n">
-        <v>2.925997972488403</v>
+        <v>2.88984227180481</v>
       </c>
       <c r="K47" t="n">
-        <v>3.174880504608154</v>
+        <v>3.003901720046997</v>
       </c>
       <c r="L47" t="n">
-        <v>2.850599837303162</v>
+        <v>2.899889206886292</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>2.339946985244751</v>
+        <v>2.303169250488281</v>
       </c>
       <c r="C48" t="n">
-        <v>2.342787265777588</v>
+        <v>2.523142337799072</v>
       </c>
       <c r="D48" t="n">
-        <v>2.372591733932495</v>
+        <v>2.391261577606201</v>
       </c>
       <c r="E48" t="n">
-        <v>2.435479640960693</v>
+        <v>2.398433446884155</v>
       </c>
       <c r="F48" t="n">
-        <v>2.290160655975342</v>
+        <v>2.354708909988403</v>
       </c>
       <c r="G48" t="n">
-        <v>2.279813528060913</v>
+        <v>2.364935159683228</v>
       </c>
       <c r="H48" t="n">
-        <v>2.275689125061035</v>
+        <v>2.45557165145874</v>
       </c>
       <c r="I48" t="n">
-        <v>2.303916454315186</v>
+        <v>2.408563852310181</v>
       </c>
       <c r="J48" t="n">
-        <v>2.236900329589844</v>
+        <v>2.340368747711182</v>
       </c>
       <c r="K48" t="n">
-        <v>2.263569116592407</v>
+        <v>2.310745716094971</v>
       </c>
       <c r="L48" t="n">
-        <v>2.314085483551025</v>
+        <v>2.385090065002442</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>2.661774635314941</v>
+        <v>2.482275485992432</v>
       </c>
       <c r="C49" t="n">
-        <v>2.544123649597168</v>
+        <v>2.390622138977051</v>
       </c>
       <c r="D49" t="n">
-        <v>2.647206783294678</v>
+        <v>2.581348180770874</v>
       </c>
       <c r="E49" t="n">
-        <v>2.447452306747437</v>
+        <v>3.936859369277954</v>
       </c>
       <c r="F49" t="n">
-        <v>2.405848026275635</v>
+        <v>2.463448524475098</v>
       </c>
       <c r="G49" t="n">
-        <v>2.400090456008911</v>
+        <v>2.497560262680054</v>
       </c>
       <c r="H49" t="n">
-        <v>2.429459095001221</v>
+        <v>2.386051177978516</v>
       </c>
       <c r="I49" t="n">
-        <v>2.441414594650269</v>
+        <v>2.487876653671265</v>
       </c>
       <c r="J49" t="n">
-        <v>2.422391176223755</v>
+        <v>2.586784839630127</v>
       </c>
       <c r="K49" t="n">
-        <v>2.525517225265503</v>
+        <v>2.432107925415039</v>
       </c>
       <c r="L49" t="n">
-        <v>2.492527794837952</v>
+        <v>2.624493455886841</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>2.188175916671753</v>
+        <v>2.180889129638672</v>
       </c>
       <c r="C50" t="n">
-        <v>2.311609983444214</v>
+        <v>2.322223901748657</v>
       </c>
       <c r="D50" t="n">
-        <v>2.170784950256348</v>
+        <v>2.296392202377319</v>
       </c>
       <c r="E50" t="n">
-        <v>2.103591918945312</v>
+        <v>2.207339763641357</v>
       </c>
       <c r="F50" t="n">
-        <v>2.15146279335022</v>
+        <v>2.317051887512207</v>
       </c>
       <c r="G50" t="n">
-        <v>2.147535800933838</v>
+        <v>2.46759819984436</v>
       </c>
       <c r="H50" t="n">
-        <v>2.294747352600098</v>
+        <v>2.328027963638306</v>
       </c>
       <c r="I50" t="n">
-        <v>2.184870004653931</v>
+        <v>2.291548252105713</v>
       </c>
       <c r="J50" t="n">
-        <v>2.358196973800659</v>
+        <v>2.289968490600586</v>
       </c>
       <c r="K50" t="n">
-        <v>2.31148886680603</v>
+        <v>2.157743215560913</v>
       </c>
       <c r="L50" t="n">
-        <v>2.22224645614624</v>
+        <v>2.285878300666809</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>2.074554920196533</v>
+        <v>2.065714120864868</v>
       </c>
       <c r="C51" t="n">
-        <v>2.041883230209351</v>
+        <v>2.101349353790283</v>
       </c>
       <c r="D51" t="n">
-        <v>2.100854396820068</v>
+        <v>2.062113761901855</v>
       </c>
       <c r="E51" t="n">
-        <v>2.051642417907715</v>
+        <v>2.03874945640564</v>
       </c>
       <c r="F51" t="n">
-        <v>2.025593757629395</v>
+        <v>2.081231832504272</v>
       </c>
       <c r="G51" t="n">
-        <v>2.104878425598145</v>
+        <v>2.182621955871582</v>
       </c>
       <c r="H51" t="n">
-        <v>2.097759246826172</v>
+        <v>2.201849460601807</v>
       </c>
       <c r="I51" t="n">
-        <v>2.194359540939331</v>
+        <v>2.144730091094971</v>
       </c>
       <c r="J51" t="n">
-        <v>2.204522132873535</v>
+        <v>2.151180744171143</v>
       </c>
       <c r="K51" t="n">
-        <v>2.093310117721558</v>
+        <v>2.070101737976074</v>
       </c>
       <c r="L51" t="n">
-        <v>2.09893581867218</v>
+        <v>2.10996425151825</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>2.297805724143982</v>
+        <v>2.33540454864502</v>
       </c>
       <c r="C52" t="n">
-        <v>2.31403799533844</v>
+        <v>2.3799689245224</v>
       </c>
       <c r="D52" t="n">
-        <v>2.292076506614685</v>
+        <v>2.359762263298035</v>
       </c>
       <c r="E52" t="n">
-        <v>2.318350467681885</v>
+        <v>2.37911169052124</v>
       </c>
       <c r="F52" t="n">
-        <v>2.291516914367676</v>
+        <v>2.33042685508728</v>
       </c>
       <c r="G52" t="n">
-        <v>2.333539786338806</v>
+        <v>2.36822952747345</v>
       </c>
       <c r="H52" t="n">
-        <v>2.286868872642517</v>
+        <v>2.390065898895264</v>
       </c>
       <c r="I52" t="n">
-        <v>2.285795435905456</v>
+        <v>2.362869668006897</v>
       </c>
       <c r="J52" t="n">
-        <v>2.290420074462891</v>
+        <v>2.391486563682556</v>
       </c>
       <c r="K52" t="n">
-        <v>2.272232360839844</v>
+        <v>2.360864777565002</v>
       </c>
       <c r="L52" t="n">
-        <v>2.298264413833618</v>
+        <v>2.365819071769714</v>
       </c>
     </row>
   </sheetData>
